--- a/data/data_LabourForce_集計加工用.xlsx
+++ b/data/data_LabourForce_集計加工用.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1619A81-7C1B-4762-A90A-C5D31EBD6C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{D1619A81-7C1B-4762-A90A-C5D31EBD6C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2A5D832-4BA4-463F-AC1D-7FA3CFF0CD96}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{42002C09-DB0D-4CC9-9E01-26328C05B93E}"/>
+    <workbookView xWindow="29040" yWindow="465" windowWidth="23310" windowHeight="14085" xr2:uid="{42002C09-DB0D-4CC9-9E01-26328C05B93E}"/>
   </bookViews>
   <sheets>
     <sheet name="data_LabourForce" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="43">
   <si>
     <t>Y</t>
     <phoneticPr fontId="1"/>
@@ -226,6 +226,14 @@
     <t>PG_TFP</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>H_M</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>H_SNA</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -365,7 +373,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -456,6 +464,12 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -658,7 +672,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>集計加工用!$AN$2:$AN$47</c:f>
+              <c:f>集計加工用!$AP$2:$AP$47</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="46"/>
@@ -1167,7 +1181,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>集計加工用!$AF$2:$AF$47</c:f>
+              <c:f>集計加工用!$AH$2:$AH$47</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="46"/>
@@ -3675,13 +3689,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>42</xdr:col>
+      <xdr:col>44</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>49</xdr:col>
+      <xdr:col>51</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>22860</xdr:rowOff>
@@ -3713,13 +3727,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>42</xdr:col>
+      <xdr:col>44</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>49</xdr:col>
+      <xdr:col>51</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>22860</xdr:rowOff>
@@ -3751,13 +3765,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>42</xdr:col>
+      <xdr:col>44</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>49</xdr:col>
+      <xdr:col>51</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>58</xdr:row>
       <xdr:rowOff>22860</xdr:rowOff>
@@ -3791,9 +3805,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3831,7 +3845,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3937,7 +3951,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4079,7 +4093,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4154,75 +4168,75 @@
         <v>1995</v>
       </c>
       <c r="B2">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>530463.19999999995</v>
       </c>
       <c r="C2">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>274056.59999999998</v>
       </c>
       <c r="D2">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>125366.79999999999</v>
       </c>
       <c r="E2">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>124557.09999999999</v>
       </c>
       <c r="F2">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>114170.09999999998</v>
       </c>
       <c r="G2">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>111.6</v>
       </c>
       <c r="H2">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>105.2</v>
       </c>
       <c r="I2">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.5</v>
       </c>
       <c r="J2">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.8</v>
       </c>
       <c r="K2">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>105556</v>
       </c>
       <c r="L2">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6666</v>
       </c>
       <c r="M2">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6457</v>
       </c>
       <c r="N2">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>210</v>
       </c>
       <c r="O2">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>93.293718166383712</v>
       </c>
       <c r="P2">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>117.8</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>115.17469190537221</v>
       </c>
       <c r="Q2">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>95.9</v>
       </c>
       <c r="R2">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>3.5058333333333298</v>
       </c>
       <c r="S2">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.7517662170841364</v>
       </c>
     </row>
@@ -4231,75 +4245,75 @@
         <v>1996</v>
       </c>
       <c r="B3">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>546227.9</v>
       </c>
       <c r="C3">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>279898</v>
       </c>
       <c r="D3">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>134570.9</v>
       </c>
       <c r="E3">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>129736.7</v>
       </c>
       <c r="F3">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>115264.80000000005</v>
       </c>
       <c r="G3">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>111.5</v>
       </c>
       <c r="H3">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>105.4</v>
       </c>
       <c r="I3">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.5</v>
       </c>
       <c r="J3">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.8</v>
       </c>
       <c r="K3">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>106173</v>
       </c>
       <c r="L3">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6711</v>
       </c>
       <c r="M3">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6486</v>
       </c>
       <c r="N3">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>225</v>
       </c>
       <c r="O3">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>94.232400339270555</v>
       </c>
       <c r="P3">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>117.9</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>115.41575265232549</v>
       </c>
       <c r="Q3">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>96</v>
       </c>
       <c r="R3">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>2.6575833333333301</v>
       </c>
       <c r="S3">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.5187823202263682</v>
       </c>
     </row>
@@ -4308,75 +4322,75 @@
         <v>1997</v>
       </c>
       <c r="B4">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>554111.80000000005</v>
       </c>
       <c r="C4">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>284813.7</v>
       </c>
       <c r="D4">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>135287</v>
       </c>
       <c r="E4">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>128663.40000000001</v>
       </c>
       <c r="F4">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>126647.30000000005</v>
       </c>
       <c r="G4">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>111.6</v>
       </c>
       <c r="H4">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>106.7</v>
       </c>
       <c r="I4">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.3</v>
       </c>
       <c r="J4">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.7</v>
       </c>
       <c r="K4">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>106791</v>
       </c>
       <c r="L4">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6787</v>
       </c>
       <c r="M4">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6557</v>
       </c>
       <c r="N4">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>230</v>
       </c>
       <c r="O4">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>97.076526225279451</v>
       </c>
       <c r="P4">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>116.3</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>113.73762097014865</v>
       </c>
       <c r="Q4">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>97.7</v>
       </c>
       <c r="R4">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>2.4488333333333299</v>
       </c>
       <c r="S4">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.3500090793535469</v>
       </c>
     </row>
@@ -4385,75 +4399,75 @@
         <v>1998</v>
       </c>
       <c r="B5">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>543304</v>
       </c>
       <c r="C5">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>283238.3</v>
       </c>
       <c r="D5">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>123964</v>
       </c>
       <c r="E5">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>126742.9</v>
       </c>
       <c r="F5">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>129640.5</v>
       </c>
       <c r="G5">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>111.4</v>
       </c>
       <c r="H5">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>106.8</v>
       </c>
       <c r="I5">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="J5">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.7</v>
       </c>
       <c r="K5">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>107413</v>
       </c>
       <c r="L5">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6793</v>
       </c>
       <c r="M5">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6514</v>
       </c>
       <c r="N5">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>279</v>
       </c>
       <c r="O5">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>96.869565217391312</v>
       </c>
       <c r="P5">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>115</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>112.44018361662494</v>
       </c>
       <c r="Q5">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>98.3</v>
       </c>
       <c r="R5">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>2.3209166666666698</v>
       </c>
       <c r="S5">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.3670197537933009</v>
       </c>
     </row>
@@ -4462,75 +4476,75 @@
         <v>1999</v>
       </c>
       <c r="B6">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>534107.1</v>
       </c>
       <c r="C6">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>284604.09999999998</v>
       </c>
       <c r="D6">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>111656.6</v>
       </c>
       <c r="E6">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>130002.3</v>
       </c>
       <c r="F6">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>122474.09999999998</v>
       </c>
       <c r="G6">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>109.9</v>
       </c>
       <c r="H6">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>106.1</v>
       </c>
       <c r="I6">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1</v>
       </c>
       <c r="J6">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.8</v>
       </c>
       <c r="K6">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>107925</v>
       </c>
       <c r="L6">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6779</v>
       </c>
       <c r="M6">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6462</v>
       </c>
       <c r="N6">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>317</v>
       </c>
       <c r="O6">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>96.481970096745812</v>
       </c>
       <c r="P6">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>113.7</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>111.46218977563225</v>
       </c>
       <c r="Q6">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>98</v>
       </c>
       <c r="R6">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>2.1608333333333301</v>
       </c>
       <c r="S6">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.4851130983692757</v>
       </c>
     </row>
@@ -4539,75 +4553,75 @@
         <v>2000</v>
       </c>
       <c r="B7">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>543394.80000000005</v>
       </c>
       <c r="C7">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>286394.8</v>
       </c>
       <c r="D7">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>120845.6</v>
       </c>
       <c r="E7">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>128848</v>
       </c>
       <c r="F7">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>117304.00000000006</v>
       </c>
       <c r="G7">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>108.6</v>
       </c>
       <c r="H7">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>105.1</v>
       </c>
       <c r="I7">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1</v>
       </c>
       <c r="J7">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.9</v>
       </c>
       <c r="K7">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>108454</v>
       </c>
       <c r="L7">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6766</v>
       </c>
       <c r="M7">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6446</v>
       </c>
       <c r="N7">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>320</v>
       </c>
       <c r="O7">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>95.895196506550221</v>
       </c>
       <c r="P7">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>114.5</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>111.81760776843626</v>
       </c>
       <c r="Q7">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>97.3</v>
       </c>
       <c r="R7">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>2.0671666666666701</v>
       </c>
       <c r="S7">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.431140130587645</v>
       </c>
     </row>
@@ -4616,75 +4630,75 @@
         <v>2001</v>
       </c>
       <c r="B8">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>539441.6</v>
       </c>
       <c r="C8">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>288170.90000000002</v>
       </c>
       <c r="D8">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>118323.6</v>
       </c>
       <c r="E8">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>129789.2</v>
       </c>
       <c r="F8">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>126951.59999999998</v>
       </c>
       <c r="G8">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>107.5</v>
       </c>
       <c r="H8">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>103.7</v>
       </c>
       <c r="I8">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.9</v>
       </c>
       <c r="J8">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="K8">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>109033</v>
       </c>
       <c r="L8">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6752</v>
       </c>
       <c r="M8">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6412</v>
       </c>
       <c r="N8">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>340</v>
       </c>
       <c r="O8">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>95.410414827890548</v>
       </c>
       <c r="P8">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>113.3</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>110.92678083076923</v>
       </c>
       <c r="Q8">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>96.7</v>
       </c>
       <c r="R8">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.9694166666666699</v>
       </c>
       <c r="S8">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.3308491861149248</v>
       </c>
     </row>
@@ -4693,75 +4707,75 @@
         <v>2002</v>
       </c>
       <c r="B9">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>532390.80000000005</v>
       </c>
       <c r="C9">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>287665.90000000002</v>
       </c>
       <c r="D9">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>108975.2</v>
       </c>
       <c r="E9">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>129121.4</v>
       </c>
       <c r="F9">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>124845.70000000007</v>
       </c>
       <c r="G9">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>106</v>
       </c>
       <c r="H9">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>102.2</v>
       </c>
       <c r="I9">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.9</v>
       </c>
       <c r="J9">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="K9">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>109384</v>
       </c>
       <c r="L9">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6689</v>
       </c>
       <c r="M9">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6330</v>
       </c>
       <c r="N9">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>359</v>
       </c>
       <c r="O9">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>93.49376114081997</v>
       </c>
       <c r="P9">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>112.2</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>110.15114467281128</v>
       </c>
       <c r="Q9">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>95.8</v>
       </c>
       <c r="R9">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.8649166666666701</v>
       </c>
       <c r="S9">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.2982595723520591</v>
       </c>
     </row>
@@ -4770,75 +4784,75 @@
         <v>2003</v>
       </c>
       <c r="B10">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>530211.80000000005</v>
       </c>
       <c r="C10">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>286411.7</v>
       </c>
       <c r="D10">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>108871</v>
       </c>
       <c r="E10">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>126516.90000000001</v>
       </c>
       <c r="F10">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>117683.00000000006</v>
       </c>
       <c r="G10">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>104.1</v>
       </c>
       <c r="H10">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>101.1</v>
       </c>
       <c r="I10">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.9</v>
       </c>
       <c r="J10">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="K10">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>109789</v>
       </c>
       <c r="L10">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6666</v>
       </c>
       <c r="M10">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6316</v>
       </c>
       <c r="N10">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>350</v>
       </c>
       <c r="O10">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>92.780748663101605</v>
       </c>
       <c r="P10">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>112.2</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>110.39588503769362</v>
       </c>
       <c r="Q10">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>95.5</v>
       </c>
       <c r="R10">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.8220833333333299</v>
       </c>
       <c r="S10">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.2955047160345214</v>
       </c>
     </row>
@@ -4847,75 +4861,75 @@
         <v>2004</v>
       </c>
       <c r="B11">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>534634.1</v>
       </c>
       <c r="C11">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>288414.09999999998</v>
       </c>
       <c r="D11">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>112132.40000000001</v>
       </c>
       <c r="E11">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>123987.4</v>
       </c>
       <c r="F11">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>115591.59999999998</v>
       </c>
       <c r="G11">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>102.8</v>
       </c>
       <c r="H11">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>100.6</v>
       </c>
       <c r="I11">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.9</v>
       </c>
       <c r="J11">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1</v>
       </c>
       <c r="K11">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>110053</v>
       </c>
       <c r="L11">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6642</v>
       </c>
       <c r="M11">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6329</v>
       </c>
       <c r="N11">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>313</v>
       </c>
       <c r="O11">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>92.170818505338076</v>
       </c>
       <c r="P11">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>112.4</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>110.93583377116521</v>
       </c>
       <c r="Q11">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>95.5</v>
       </c>
       <c r="R11">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.7665833333333301</v>
       </c>
       <c r="S11">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.2689973995954926</v>
       </c>
     </row>
@@ -4924,75 +4938,75 @@
         <v>2005</v>
       </c>
       <c r="B12">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>537385.19999999995</v>
       </c>
       <c r="C12">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>290679.3</v>
       </c>
       <c r="D12">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>116899.59999999999</v>
       </c>
       <c r="E12">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>122348.6</v>
       </c>
       <c r="F12">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>119292.19999999995</v>
       </c>
       <c r="G12">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>101.5</v>
       </c>
       <c r="H12">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>99.7</v>
       </c>
       <c r="I12">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.8</v>
       </c>
       <c r="J12">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.8</v>
       </c>
       <c r="K12">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>110247</v>
       </c>
       <c r="L12">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6651</v>
       </c>
       <c r="M12">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6356</v>
       </c>
       <c r="N12">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>294</v>
       </c>
       <c r="O12">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>93.375111906893466</v>
       </c>
       <c r="P12">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>111.7</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>110.28131846733939</v>
       </c>
       <c r="Q12">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>95.2</v>
       </c>
       <c r="R12">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.6769166666666699</v>
       </c>
       <c r="S12">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.1309939528149184</v>
       </c>
     </row>
@@ -5001,75 +5015,75 @@
         <v>2006</v>
       </c>
       <c r="B13">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>540566</v>
       </c>
       <c r="C13">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>293508.59999999998</v>
       </c>
       <c r="D13">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>119256.30000000002</v>
       </c>
       <c r="E13">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>120862.90000000001</v>
       </c>
       <c r="F13">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>115174.40000000002</v>
       </c>
       <c r="G13">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>100.5</v>
       </c>
       <c r="H13">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>99.7</v>
       </c>
       <c r="I13">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.6</v>
       </c>
       <c r="J13">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.7</v>
       </c>
       <c r="K13">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>110466</v>
       </c>
       <c r="L13">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6664</v>
       </c>
       <c r="M13">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6389</v>
       </c>
       <c r="N13">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>275</v>
       </c>
       <c r="O13">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>93.137254901960787</v>
       </c>
       <c r="P13">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>112.2</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>110.68616202764865</v>
       </c>
       <c r="Q13">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>95.5</v>
       </c>
       <c r="R13">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.6648333333333301</v>
       </c>
       <c r="S13">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.98504561088679232</v>
       </c>
     </row>
@@ -5078,75 +5092,75 @@
         <v>2007</v>
       </c>
       <c r="B14">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>544571.1</v>
       </c>
       <c r="C14">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>294745.09999999998</v>
       </c>
       <c r="D14">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>119838.3</v>
       </c>
       <c r="E14">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>120498.79999999999</v>
       </c>
       <c r="F14">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>118188.5</v>
       </c>
       <c r="G14">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>99.5</v>
       </c>
       <c r="H14">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>99.3</v>
       </c>
       <c r="I14">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.4</v>
       </c>
       <c r="J14">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.6</v>
       </c>
       <c r="K14">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>110740</v>
       </c>
       <c r="L14">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6684</v>
       </c>
       <c r="M14">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6427</v>
       </c>
       <c r="N14">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>257</v>
       </c>
       <c r="O14">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>92.908438061041281</v>
       </c>
       <c r="P14">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>111.4</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>109.98496258143892</v>
       </c>
       <c r="Q14">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>95.5</v>
       </c>
       <c r="R14">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.8832500000000001</v>
       </c>
       <c r="S14">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.91822543633961506</v>
       </c>
     </row>
@@ -5155,75 +5169,75 @@
         <v>2008</v>
       </c>
       <c r="B15">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>533355.4</v>
       </c>
       <c r="C15">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>293475.40000000002</v>
       </c>
       <c r="D15">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>118293.79999999999</v>
       </c>
       <c r="E15">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>119792.19999999998</v>
       </c>
       <c r="F15">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>139816.80000000005</v>
       </c>
       <c r="G15">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>98.6</v>
       </c>
       <c r="H15">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>100</v>
       </c>
       <c r="I15">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.1</v>
       </c>
       <c r="J15">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.6</v>
       </c>
       <c r="K15">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>110908</v>
       </c>
       <c r="L15">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6674</v>
       </c>
       <c r="M15">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6409</v>
       </c>
       <c r="N15">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>265</v>
       </c>
       <c r="O15">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>93.738656987295826</v>
       </c>
       <c r="P15">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>110.2</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>108.69178178681196</v>
       </c>
       <c r="Q15">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>96.8</v>
       </c>
       <c r="R15">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.9095</v>
       </c>
       <c r="S15">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.86304264310411061</v>
       </c>
     </row>
@@ -5232,75 +5246,75 @@
         <v>2009</v>
       </c>
       <c r="B16">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>499361.7</v>
       </c>
       <c r="C16">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>283897.2</v>
       </c>
       <c r="D16">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>91724.6</v>
       </c>
       <c r="E16">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>121523.2</v>
       </c>
       <c r="F16">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>118820.79999999999</v>
       </c>
       <c r="G16">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>98.2</v>
       </c>
       <c r="H16">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>97.6</v>
       </c>
       <c r="I16">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.1</v>
       </c>
       <c r="J16">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.7</v>
       </c>
       <c r="K16">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>111021</v>
       </c>
       <c r="L16">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6650</v>
       </c>
       <c r="M16">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6314</v>
       </c>
       <c r="N16">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>336</v>
       </c>
       <c r="O16">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>92.803738317757009</v>
       </c>
       <c r="P16">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>107</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>105.72077611315964</v>
       </c>
       <c r="Q16">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>95.5</v>
       </c>
       <c r="R16">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.7233333333333301</v>
       </c>
       <c r="S16">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.1187676993049038</v>
       </c>
     </row>
@@ -5309,75 +5323,75 @@
         <v>2010</v>
       </c>
       <c r="B17">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>510139.6</v>
       </c>
       <c r="C17">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>286441</v>
       </c>
       <c r="D17">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>94525.000000000015</v>
       </c>
       <c r="E17">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>122411.90000000001</v>
       </c>
       <c r="F17">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>116293.29999999999</v>
       </c>
       <c r="G17">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>96.3</v>
       </c>
       <c r="H17">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>96.2</v>
       </c>
       <c r="I17">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.3</v>
       </c>
       <c r="J17">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.9</v>
       </c>
       <c r="K17">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>111254</v>
       </c>
       <c r="L17">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6632</v>
       </c>
       <c r="M17">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6298</v>
       </c>
       <c r="N17">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>334</v>
       </c>
       <c r="O17">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>91.988950276243102</v>
       </c>
       <c r="P17">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>108.6</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>106.88312336387678</v>
       </c>
       <c r="Q17">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>94.8</v>
       </c>
       <c r="R17">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.5983333333333301</v>
       </c>
       <c r="S17">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.0669016905696724</v>
       </c>
     </row>
@@ -5386,75 +5400,75 @@
         <v>2011</v>
       </c>
       <c r="B18">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>501142</v>
       </c>
       <c r="C18">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>283221.5</v>
       </c>
       <c r="D18">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>98202.3</v>
       </c>
       <c r="E18">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>122937.1</v>
       </c>
       <c r="F18">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>113477.5</v>
       </c>
       <c r="G18">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>94.8</v>
       </c>
       <c r="H18">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>95.7</v>
       </c>
       <c r="I18">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.5</v>
       </c>
       <c r="J18">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="K18">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>111129</v>
       </c>
       <c r="L18">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6596</v>
       </c>
       <c r="M18">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6293</v>
       </c>
       <c r="N18">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>302</v>
       </c>
       <c r="O18">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>92.059095106186533</v>
       </c>
       <c r="P18">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>108.3</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>106.5405935511082</v>
       </c>
       <c r="Q18">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>94.5</v>
       </c>
       <c r="R18">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.50091666666667</v>
       </c>
       <c r="S18">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.0234811777860604</v>
       </c>
     </row>
@@ -5463,75 +5477,75 @@
         <v>2012</v>
       </c>
       <c r="B19">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>505377.1</v>
       </c>
       <c r="C19">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>287611.09999999998</v>
       </c>
       <c r="D19">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>101490.5</v>
       </c>
       <c r="E19">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>124495.2</v>
       </c>
       <c r="F19">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>116089.5</v>
       </c>
       <c r="G19">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>94.1</v>
       </c>
       <c r="H19">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>95.1</v>
       </c>
       <c r="I19">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.7</v>
       </c>
       <c r="J19">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.2</v>
       </c>
       <c r="K19">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>111046</v>
       </c>
       <c r="L19">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6565</v>
       </c>
       <c r="M19">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6280</v>
       </c>
       <c r="N19">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>285</v>
       </c>
       <c r="O19">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>90.725436179981628</v>
       </c>
       <c r="P19">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>108.9</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>107.30591545242444</v>
       </c>
       <c r="Q19">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>94.5</v>
       </c>
       <c r="R19">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.4075</v>
       </c>
       <c r="S19">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.0106820049301593</v>
       </c>
     </row>
@@ -5540,75 +5554,75 @@
         <v>2013</v>
       </c>
       <c r="B20">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>514553.3</v>
       </c>
       <c r="C20">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>295249.40000000002</v>
       </c>
       <c r="D20">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>104172.8</v>
       </c>
       <c r="E20">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>127397.7</v>
       </c>
       <c r="F20">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>109296.29999999999</v>
       </c>
       <c r="G20">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>93.9</v>
       </c>
       <c r="H20">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>95</v>
       </c>
       <c r="I20">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1</v>
       </c>
       <c r="J20">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.2</v>
       </c>
       <c r="K20">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>111024</v>
       </c>
       <c r="L20">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6593</v>
       </c>
       <c r="M20">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6326</v>
       </c>
       <c r="N20">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>265</v>
       </c>
       <c r="O20">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>91.457753017641593</v>
       </c>
       <c r="P20">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>107.7</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>106.20018909079735</v>
       </c>
       <c r="Q20">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>94.9</v>
       </c>
       <c r="R20">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.30375</v>
       </c>
       <c r="S20">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.86688417618270763</v>
       </c>
     </row>
@@ -5617,75 +5631,75 @@
         <v>2014</v>
       </c>
       <c r="B21">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>528215.6</v>
       </c>
       <c r="C21">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>299134.2</v>
       </c>
       <c r="D21">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>111396.7</v>
       </c>
       <c r="E21">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>131146.9</v>
       </c>
       <c r="F21">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>111857.5</v>
       </c>
       <c r="G21">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>95.5</v>
       </c>
       <c r="H21">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>96.9</v>
       </c>
       <c r="I21">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="J21">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1</v>
       </c>
       <c r="K21">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>111004</v>
       </c>
       <c r="L21">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6609</v>
       </c>
       <c r="M21">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6371</v>
       </c>
       <c r="N21">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>236</v>
       </c>
       <c r="O21">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>92.264678471575024</v>
       </c>
       <c r="P21">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>107.3</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>105.96549576186771</v>
       </c>
       <c r="Q21">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>97.5</v>
       </c>
       <c r="R21">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.2191666666666701</v>
       </c>
       <c r="S21">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.81684408265497765</v>
       </c>
     </row>
@@ -5694,75 +5708,75 @@
         <v>2015</v>
       </c>
       <c r="B22">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>548866.69999999995</v>
       </c>
       <c r="C22">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>300946.59999999998</v>
       </c>
       <c r="D22">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>118870.39999999999</v>
       </c>
       <c r="E22">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>132032.30000000002</v>
       </c>
       <c r="F22">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>112482.29999999993</v>
       </c>
       <c r="G22">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>97.5</v>
       </c>
       <c r="H22">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>97.4</v>
       </c>
       <c r="I22">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1</v>
       </c>
       <c r="J22">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.8</v>
       </c>
       <c r="K22">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>111208</v>
       </c>
       <c r="L22">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6625</v>
       </c>
       <c r="M22">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6402</v>
       </c>
       <c r="N22">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>222</v>
       </c>
       <c r="O22">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>92.703461178671645</v>
       </c>
       <c r="P22">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>106.9</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>105.54785363345115</v>
       </c>
       <c r="Q22">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>98.2</v>
       </c>
       <c r="R22">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.14283333333333</v>
       </c>
       <c r="S22">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.8689854663468326</v>
       </c>
     </row>
@@ -5771,75 +5785,75 @@
         <v>2016</v>
       </c>
       <c r="B23">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>555970.6</v>
       </c>
       <c r="C23">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>298979.90000000002</v>
       </c>
       <c r="D23">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>118815.2</v>
       </c>
       <c r="E23">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>133791.5</v>
       </c>
       <c r="F23">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>120822</v>
       </c>
       <c r="G23">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>98.1</v>
       </c>
       <c r="H23">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>97.1</v>
       </c>
       <c r="I23">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.9</v>
       </c>
       <c r="J23">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.6</v>
       </c>
       <c r="K23">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>111233</v>
       </c>
       <c r="L23">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6678</v>
       </c>
       <c r="M23">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6470</v>
       </c>
       <c r="N23">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>208</v>
       </c>
       <c r="O23">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>93.791157102539984</v>
       </c>
       <c r="P23">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>106.3</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>105.10387255783979</v>
       </c>
       <c r="Q23">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>98.1</v>
       </c>
       <c r="R23">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.0447500000000001</v>
       </c>
       <c r="S23">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.0072604474461802</v>
       </c>
     </row>
@@ -5848,75 +5862,75 @@
         <v>2017</v>
       </c>
       <c r="B24">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>565119</v>
       </c>
       <c r="C24">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>303099.90000000002</v>
       </c>
       <c r="D24">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>122919</v>
       </c>
       <c r="E24">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>134902.20000000001</v>
       </c>
       <c r="F24">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>121413.40000000002</v>
       </c>
       <c r="G24">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>98.1</v>
       </c>
       <c r="H24">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>97.6</v>
       </c>
       <c r="I24">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.7</v>
       </c>
       <c r="J24">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.4</v>
       </c>
       <c r="K24">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>111278</v>
       </c>
       <c r="L24">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6732</v>
       </c>
       <c r="M24">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6542</v>
       </c>
       <c r="N24">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>190</v>
       </c>
       <c r="O24">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>94.439208294062212</v>
       </c>
       <c r="P24">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>106.1</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>105.17208576035692</v>
       </c>
       <c r="Q24">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>98.6</v>
       </c>
       <c r="R24">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.96941666666666704</v>
       </c>
       <c r="S24">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.93852240736514037</v>
       </c>
     </row>
@@ -5925,75 +5939,75 @@
         <v>2018</v>
       </c>
       <c r="B25">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>569153.5</v>
       </c>
       <c r="C25">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>305863</v>
       </c>
       <c r="D25">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>126171.90000000001</v>
       </c>
       <c r="E25">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>137012</v>
       </c>
       <c r="F25">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>119200</v>
       </c>
       <c r="G25">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>98</v>
       </c>
       <c r="H25">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>98.3</v>
       </c>
       <c r="I25">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.5</v>
       </c>
       <c r="J25">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.4</v>
       </c>
       <c r="K25">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>111276</v>
       </c>
       <c r="L25">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6849</v>
       </c>
       <c r="M25">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6682</v>
       </c>
       <c r="N25">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>167</v>
       </c>
       <c r="O25">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>96.577946768060826</v>
       </c>
       <c r="P25">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>105.2</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>104.11521257191903</v>
       </c>
       <c r="Q25">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>99.5</v>
       </c>
       <c r="R25">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.92174999999999996</v>
       </c>
       <c r="S25">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.8909489774255237</v>
       </c>
     </row>
@@ -6002,75 +6016,75 @@
         <v>2019</v>
       </c>
       <c r="B26">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>571838</v>
       </c>
       <c r="C26">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>306008.7</v>
       </c>
       <c r="D26">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>127001.5</v>
       </c>
       <c r="E26">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>140444.4</v>
       </c>
       <c r="F26">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>126747.59999999998</v>
       </c>
       <c r="G26">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>98.7</v>
       </c>
       <c r="H26">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>99.1</v>
       </c>
       <c r="I26">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.4</v>
       </c>
       <c r="J26">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.4</v>
       </c>
       <c r="K26">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>111296</v>
       </c>
       <c r="L26">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6912</v>
       </c>
       <c r="M26">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6750</v>
       </c>
       <c r="N26">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>162</v>
       </c>
       <c r="O26">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>98.347910592808546</v>
       </c>
       <c r="P26">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>102.9</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>102.25995145350291</v>
       </c>
       <c r="Q26">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>100</v>
       </c>
       <c r="R26">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.88100000000000001</v>
       </c>
       <c r="S26">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.91534668260610252</v>
       </c>
     </row>
@@ -6079,75 +6093,75 @@
         <v>2020</v>
       </c>
       <c r="B27">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>554074.4</v>
       </c>
       <c r="C27">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>293314.5</v>
       </c>
       <c r="D27">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>118258.7</v>
       </c>
       <c r="E27">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>143952</v>
       </c>
       <c r="F27">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>131804.10000000003</v>
       </c>
       <c r="G27">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>100</v>
       </c>
       <c r="H27">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>100</v>
       </c>
       <c r="I27">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.4</v>
       </c>
       <c r="J27">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.5</v>
       </c>
       <c r="K27">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>111114</v>
       </c>
       <c r="L27">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6902</v>
       </c>
       <c r="M27">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6710</v>
       </c>
       <c r="N27">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>192</v>
       </c>
       <c r="O27">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>100</v>
       </c>
       <c r="P27">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>100</v>
       </c>
       <c r="Q27">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>100</v>
       </c>
       <c r="R27">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.82666666666666699</v>
       </c>
       <c r="S27">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.99991667361053582</v>
       </c>
     </row>
@@ -6156,75 +6170,75 @@
         <v>2021</v>
       </c>
       <c r="B28">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>573568.80000000005</v>
       </c>
       <c r="C28">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>301948.2</v>
       </c>
       <c r="D28">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>126185.9</v>
       </c>
       <c r="E28">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>148310.69999999998</v>
       </c>
       <c r="F28">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>125301.30000000005</v>
       </c>
       <c r="G28">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>99.9</v>
       </c>
       <c r="H28">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>101</v>
       </c>
       <c r="I28">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.4</v>
       </c>
       <c r="J28">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.6</v>
       </c>
       <c r="K28">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>110735</v>
       </c>
       <c r="L28">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6907</v>
       </c>
       <c r="M28">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6713</v>
       </c>
       <c r="N28">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>195</v>
       </c>
       <c r="O28">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>99.602780536246271</v>
       </c>
       <c r="P28">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>100.7</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>101.15693191092603</v>
       </c>
       <c r="Q28">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>99.8</v>
       </c>
       <c r="R28">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.80408333333333304</v>
       </c>
       <c r="S28">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.87010761532661318</v>
       </c>
     </row>
@@ -6233,75 +6247,75 @@
         <v>2022</v>
       </c>
       <c r="B29">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>584900.6</v>
       </c>
       <c r="C29">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>319026.8</v>
       </c>
       <c r="D29">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>136419.5</v>
       </c>
       <c r="E29">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>150305.5</v>
       </c>
       <c r="F29">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>122603.89999999997</v>
       </c>
       <c r="G29">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>100.6</v>
       </c>
       <c r="H29">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>104.3</v>
       </c>
       <c r="I29">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.5</v>
       </c>
       <c r="J29">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.6</v>
       </c>
       <c r="K29">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>110463</v>
       </c>
       <c r="L29">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6902</v>
       </c>
       <c r="M29">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6723</v>
       </c>
       <c r="N29">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>179</v>
       </c>
       <c r="O29">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>101.48809523809523</v>
       </c>
       <c r="P29">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>100.8</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>100.97772178061501</v>
       </c>
       <c r="Q29">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>102.3</v>
       </c>
       <c r="R29">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.78349999999999997</v>
       </c>
       <c r="S29">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.65492090089202171</v>
       </c>
     </row>
@@ -6310,75 +6324,75 @@
         <v>2023</v>
       </c>
       <c r="B30">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>616033</v>
       </c>
       <c r="C30">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>330179.7</v>
       </c>
       <c r="D30">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>140353.29999999999</v>
       </c>
       <c r="E30">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>154595.4</v>
       </c>
       <c r="F30">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>133596.20000000001</v>
       </c>
       <c r="G30">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>105.1</v>
       </c>
       <c r="H30">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>107.9</v>
       </c>
       <c r="I30">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.4</v>
       </c>
       <c r="J30">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.5</v>
       </c>
       <c r="K30">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>110206</v>
       </c>
       <c r="L30">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6925</v>
       </c>
       <c r="M30">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6747</v>
       </c>
       <c r="N30">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>178</v>
       </c>
       <c r="O30">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>102.57680872150642</v>
       </c>
       <c r="P30">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>100.9</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>101.10061589869525</v>
       </c>
       <c r="Q30">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>105.6</v>
       </c>
       <c r="R30">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.77691666666666703</v>
       </c>
       <c r="S30">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.68550012923235915</v>
       </c>
     </row>
@@ -6387,75 +6401,75 @@
         <v>2024</v>
       </c>
       <c r="B31">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>634226</v>
       </c>
       <c r="C31">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>336580.9</v>
       </c>
       <c r="D31">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>144166.6</v>
       </c>
       <c r="E31">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>159143</v>
       </c>
       <c r="F31">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>137572.09999999998</v>
       </c>
       <c r="G31">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>108.5</v>
       </c>
       <c r="H31">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>110.6</v>
       </c>
       <c r="I31">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.4</v>
       </c>
       <c r="J31">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.4</v>
       </c>
       <c r="K31">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>109929</v>
       </c>
       <c r="L31">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6957</v>
       </c>
       <c r="M31">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6781</v>
       </c>
       <c r="N31">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>176</v>
       </c>
       <c r="O31">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>106.51410036940263</v>
       </c>
       <c r="P31">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>99.891000000000005</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>100.15188070898171</v>
       </c>
       <c r="Q31">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>108.5</v>
       </c>
       <c r="R31">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.84183333333333299</v>
       </c>
       <c r="S31">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.68019129121570465</v>
       </c>
     </row>
@@ -6464,75 +6478,75 @@
         <v>2025</v>
       </c>
       <c r="B32">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>663757.30000000005</v>
       </c>
       <c r="C32">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>351588</v>
       </c>
       <c r="D32">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>151590</v>
       </c>
       <c r="E32">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>164108.20000000001</v>
       </c>
       <c r="F32">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>151540.05198156688</v>
       </c>
       <c r="G32">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>112.2</v>
       </c>
       <c r="H32">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>113.9</v>
       </c>
       <c r="I32">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.4</v>
       </c>
       <c r="J32">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.3</v>
       </c>
       <c r="K32">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>109629</v>
       </c>
       <c r="L32">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>7004</v>
       </c>
       <c r="M32">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>6828</v>
       </c>
       <c r="N32">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>176</v>
       </c>
       <c r="O32">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>110.5110797950293</v>
       </c>
       <c r="P32">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>98.492525999999998</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>98.749754379055958</v>
       </c>
       <c r="Q32">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>111.9</v>
       </c>
       <c r="R32">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>1.1034999999999999</v>
       </c>
       <c r="S32">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.71206143811477352</v>
       </c>
     </row>
@@ -6541,75 +6555,75 @@
         <v>2026</v>
       </c>
       <c r="B33">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>686325.04820000008</v>
       </c>
       <c r="C33">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>363541.99200000003</v>
       </c>
       <c r="D33">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>156744.06</v>
       </c>
       <c r="E33" t="str">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="F33" t="str">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="G33">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>114.444</v>
       </c>
       <c r="H33">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>116.17800000000001</v>
       </c>
       <c r="I33">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.8</v>
       </c>
       <c r="J33">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.3</v>
       </c>
       <c r="K33">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>109306</v>
       </c>
       <c r="L33" t="str">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="M33" t="str">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="N33" t="str">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="O33" t="str">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="P33">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>99.023738838709704</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>99.282354561790484</v>
       </c>
       <c r="Q33">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>114.0261</v>
       </c>
       <c r="R33" t="str">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="S33">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.71206143811477352</v>
       </c>
     </row>
@@ -6618,75 +6632,75 @@
         <v>2027</v>
       </c>
       <c r="B34">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>697306.24897120008</v>
       </c>
       <c r="C34">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>369358.663872</v>
       </c>
       <c r="D34">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>159251.96496000001</v>
       </c>
       <c r="E34" t="str">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="F34" t="str">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="G34">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>115.702884</v>
       </c>
       <c r="H34">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>117.455958</v>
       </c>
       <c r="I34">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.7</v>
       </c>
       <c r="J34">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.3</v>
       </c>
       <c r="K34">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>108944</v>
       </c>
       <c r="L34" t="str">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="M34" t="str">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="N34" t="str">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="O34" t="str">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="P34">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>98.439811424349642</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>98.696902131184189</v>
       </c>
       <c r="Q34">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>115.6224654</v>
       </c>
       <c r="R34" t="str">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="S34">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.71206143811477352</v>
       </c>
     </row>
@@ -6695,75 +6709,75 @@
         <v>2028</v>
       </c>
       <c r="B35">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>705673.92395885452</v>
       </c>
       <c r="C35">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>373790.96783846401</v>
       </c>
       <c r="D35">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>161162.98853952001</v>
       </c>
       <c r="E35" t="str">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="F35" t="str">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="G35">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>116.51280418799999</v>
       </c>
       <c r="H35">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>118.27814970599998</v>
       </c>
       <c r="I35">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.6</v>
       </c>
       <c r="J35">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.3</v>
       </c>
       <c r="K35">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>108564</v>
       </c>
       <c r="L35" t="str">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="M35" t="str">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="N35" t="str">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="O35" t="str">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="P35">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>97.908772480145018</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>98.164476297106987</v>
       </c>
       <c r="Q35">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>116.89431251939999</v>
       </c>
       <c r="R35" t="str">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="S35">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.71206143811477352</v>
       </c>
     </row>
@@ -6772,75 +6786,75 @@
         <v>2029</v>
       </c>
       <c r="B36">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>714142.01104636083</v>
       </c>
       <c r="C36">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>378276.4594525256</v>
       </c>
       <c r="D36">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>163096.94440199426</v>
       </c>
       <c r="E36" t="str">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="F36" t="str">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="G36">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>117.32839381731598</v>
       </c>
       <c r="H36">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>119.10609675394197</v>
       </c>
       <c r="I36">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.6</v>
       </c>
       <c r="J36">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.3</v>
       </c>
       <c r="K36">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>108146</v>
       </c>
       <c r="L36" t="str">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="M36" t="str">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="N36" t="str">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="O36" t="str">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="P36">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>97.321213598466571</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>97.575382915046902</v>
       </c>
       <c r="Q36">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>118.18014995711337</v>
       </c>
       <c r="R36" t="str">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="S36">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.71206143811477352</v>
       </c>
     </row>
@@ -6849,75 +6863,75 @@
         <v>2030</v>
       </c>
       <c r="B37">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>722711.71517891716</v>
       </c>
       <c r="C37">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>382815.77696595591</v>
       </c>
       <c r="D37">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>165054.10773481819</v>
       </c>
       <c r="E37" t="str">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="F37" t="str">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="G37">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>118.14969257403719</v>
       </c>
       <c r="H37">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>119.93983943121955</v>
       </c>
       <c r="I37">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.6</v>
       </c>
       <c r="J37">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.3</v>
       </c>
       <c r="K37">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>107719</v>
       </c>
       <c r="L37" t="str">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="M37" t="str">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="N37" t="str">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="O37" t="str">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="P37">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>96.68423568379643</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>96.936741434590203</v>
       </c>
       <c r="Q37">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>119.48013160664161</v>
       </c>
       <c r="R37" t="str">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="S37">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.71206143811477352</v>
       </c>
     </row>
@@ -6926,75 +6940,75 @@
         <v>2031</v>
       </c>
       <c r="B38">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>731384.25576106412</v>
       </c>
       <c r="C38">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>387409.56628954737</v>
       </c>
       <c r="D38">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>167034.75702763602</v>
       </c>
       <c r="E38" t="str">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="F38" t="str">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="G38">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>118.97674042205544</v>
       </c>
       <c r="H38">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>120.77941830723807</v>
       </c>
       <c r="I38">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.5</v>
       </c>
       <c r="J38">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.3</v>
       </c>
       <c r="K38">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>107255</v>
       </c>
       <c r="L38" t="str">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="M38" t="str">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="N38" t="str">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="O38" t="str">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="P38">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>95.98686569240455</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>96.237550154215569</v>
       </c>
       <c r="Q38">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>120.79441305431465</v>
       </c>
       <c r="R38" t="str">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="S38">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.71206143811477352</v>
       </c>
     </row>
@@ -7003,75 +7017,75 @@
         <v>2032</v>
       </c>
       <c r="B39">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>740160.86683019693</v>
       </c>
       <c r="C39">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>392058.48108502192</v>
       </c>
       <c r="D39">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>169039.17411196764</v>
       </c>
       <c r="E39" t="str">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="F39" t="str">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="G39">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>119.80957760500982</v>
       </c>
       <c r="H39">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>121.62487423538873</v>
       </c>
       <c r="I39">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.5</v>
       </c>
       <c r="J39">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.3</v>
       </c>
       <c r="K39">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>106740</v>
       </c>
       <c r="L39" t="str">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="M39" t="str">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="N39" t="str">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="O39" t="str">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="P39">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>95.366065794485991</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>95.615128941889267</v>
       </c>
       <c r="Q39">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>122.1231515979121</v>
       </c>
       <c r="R39" t="str">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="S39">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.71206143811477352</v>
       </c>
     </row>
@@ -7080,75 +7094,75 @@
         <v>2033</v>
       </c>
       <c r="B40">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>749042.7972321593</v>
       </c>
       <c r="C40">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>396763.18285804219</v>
       </c>
       <c r="D40">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>171067.64420131125</v>
       </c>
       <c r="E40" t="str">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="F40" t="str">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="G40">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>120.64824464824488</v>
       </c>
       <c r="H40">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>122.47624835503643</v>
       </c>
       <c r="I40">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.5</v>
       </c>
       <c r="J40">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.3</v>
       </c>
       <c r="K40">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>106192</v>
       </c>
       <c r="L40" t="str">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="M40" t="str">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="N40" t="str">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="O40" t="str">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="P40">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>94.699440969788242</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>94.946763123939959</v>
       </c>
       <c r="Q40">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>123.46650626548912</v>
       </c>
       <c r="R40" t="str">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="S40">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.71206143811477352</v>
       </c>
     </row>
@@ -7157,75 +7171,75 @@
         <v>2034</v>
       </c>
       <c r="B41">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>757282.26800171298</v>
       </c>
       <c r="C41">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>401127.57786948059</v>
       </c>
       <c r="D41">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>172949.38828752565</v>
       </c>
       <c r="E41" t="str">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="F41" t="str">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="G41">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>121.49278236078258</v>
       </c>
       <c r="H41">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>123.33358209352167</v>
       </c>
       <c r="I41">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.4</v>
       </c>
       <c r="J41">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.3</v>
       </c>
       <c r="K41">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>105591</v>
       </c>
       <c r="L41" t="str">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="M41" t="str">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="N41" t="str">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="O41" t="str">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="P41">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>93.984438323874741</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>94.229893138654646</v>
       </c>
       <c r="Q41">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>124.82463783440949</v>
       </c>
       <c r="R41" t="str">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="S41">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.71206143811477352</v>
       </c>
     </row>
@@ -7234,75 +7248,75 @@
         <v>2035</v>
       </c>
       <c r="B42">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>765612.37294973177</v>
       </c>
       <c r="C42">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>405539.98122604482</v>
       </c>
       <c r="D42">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>174851.83155868843</v>
       </c>
       <c r="E42" t="str">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="F42" t="str">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="G42">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>122.34323183730805</v>
       </c>
       <c r="H42">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>124.19691716817631</v>
       </c>
       <c r="I42">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.4</v>
       </c>
       <c r="J42">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.3</v>
       </c>
       <c r="K42">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>104948</v>
       </c>
       <c r="L42" t="str">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="M42" t="str">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="N42" t="str">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="O42" t="str">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="P42">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>93.290084104489878</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>93.533725506439424</v>
       </c>
       <c r="Q42">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>126.19770885058797</v>
       </c>
       <c r="R42" t="str">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="S42">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.71206143811477352</v>
       </c>
     </row>
@@ -7311,75 +7325,75 @@
         <v>2036</v>
       </c>
       <c r="B43">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>773910.88647957356</v>
       </c>
       <c r="C43">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>409935.65081028896</v>
       </c>
       <c r="D43">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>176747.05992904116</v>
       </c>
       <c r="E43" t="str">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="F43" t="str">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="G43">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>123.19963446016919</v>
       </c>
       <c r="H43">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>125.06629558835354</v>
       </c>
       <c r="I43">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.4</v>
       </c>
       <c r="J43">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.3</v>
       </c>
       <c r="K43">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>104297</v>
       </c>
       <c r="L43" t="str">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="M43" t="str">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="N43" t="str">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="O43" t="str">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="P43">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>92.637849093417458</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>92.879787083326775</v>
       </c>
       <c r="Q43">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>127.58588364794443</v>
       </c>
       <c r="R43" t="str">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="S43">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.71206143811477352</v>
       </c>
     </row>
@@ -7388,75 +7402,75 @@
         <v>2037</v>
       </c>
       <c r="B44">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>782179.41251643701</v>
       </c>
       <c r="C44">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>414315.43621114071</v>
       </c>
       <c r="D44">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>178635.4397056977</v>
       </c>
       <c r="E44" t="str">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="F44" t="str">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="G44">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>124.06203190139037</v>
       </c>
       <c r="H44">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>125.94175965747201</v>
       </c>
       <c r="I44">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.4</v>
       </c>
       <c r="J44">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.3</v>
       </c>
       <c r="K44">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>103601</v>
       </c>
       <c r="L44" t="str">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="M44" t="str">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="N44" t="str">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="O44" t="str">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="P44">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>91.975067086693841</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>92.215274119461711</v>
       </c>
       <c r="Q44">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>128.9893283680718</v>
       </c>
       <c r="R44" t="str">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="S44">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.71206143811477352</v>
       </c>
     </row>
@@ -7465,75 +7479,75 @@
         <v>2038</v>
       </c>
       <c r="B45">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>790426.73636312608</v>
       </c>
       <c r="C45">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>418683.99094735179</v>
       </c>
       <c r="D45">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>180518.97729077525</v>
       </c>
       <c r="E45" t="str">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="F45" t="str">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="G45">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>124.93046612470009</v>
       </c>
       <c r="H45">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>126.8233519750743</v>
       </c>
       <c r="I45">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.4</v>
       </c>
       <c r="J45">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.3</v>
       </c>
       <c r="K45">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>102871</v>
       </c>
       <c r="L45" t="str">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="M45" t="str">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="N45" t="str">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="O45" t="str">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="P45">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>91.385230310758033</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>91.623896894073098</v>
       </c>
       <c r="Q45">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>130.40821098012057</v>
       </c>
       <c r="R45" t="str">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="S45">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.71206143811477352</v>
       </c>
     </row>
@@ -7542,75 +7556,75 @@
         <v>2039</v>
       </c>
       <c r="B46">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>798648.3482101839</v>
       </c>
       <c r="C46">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>423038.92620167346</v>
       </c>
       <c r="D46">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>182396.64272646309</v>
       </c>
       <c r="E46" t="str">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="F46" t="str">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="G46">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>125.80497938757297</v>
       </c>
       <c r="H46">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>127.71111543889981</v>
       </c>
       <c r="I46">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.4</v>
       </c>
       <c r="J46">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.3</v>
       </c>
       <c r="K46">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>102145</v>
       </c>
       <c r="L46" t="str">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="M46" t="str">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="N46" t="str">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="O46" t="str">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="P46">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>90.792994808335706</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>91.030114677554849</v>
       </c>
       <c r="Q46">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>131.84270130090189</v>
       </c>
       <c r="R46" t="str">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="S46">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.71206143811477352</v>
       </c>
     </row>
@@ -7619,88 +7633,87 @@
         <v>2040</v>
       </c>
       <c r="B47">
-        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(B$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>806846.71671906847</v>
       </c>
       <c r="C47">
-        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(C$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>427381.54960830376</v>
       </c>
       <c r="D47">
-        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(D$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>184268.99980978528</v>
       </c>
       <c r="E47" t="str">
-        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(E$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="F47" t="str">
-        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(F$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="G47">
-        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(G$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>126.68561424328597</v>
       </c>
       <c r="H47">
-        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(H$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>128.6050932469721</v>
       </c>
       <c r="I47">
-        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(I$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.4</v>
       </c>
       <c r="J47">
-        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(J$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.3</v>
       </c>
       <c r="K47">
-        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(K$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>101418</v>
       </c>
       <c r="L47" t="str">
-        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(L$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="M47" t="str">
-        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(M$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="N47" t="str">
-        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(N$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="O47" t="str">
-        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(O$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="P47">
-        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
-        <v>90.168308077789462</v>
+        <f>IF(HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(P$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
+        <v>90.403796481539672</v>
       </c>
       <c r="Q47">
-        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(Q$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>133.2929710152118</v>
       </c>
       <c r="R47" t="str">
-        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(R$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>NA</v>
       </c>
       <c r="S47">
-        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AN$47,ROW(),FALSE))</f>
+        <f>IF(HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE)=0,"NA",HLOOKUP(S$1,集計加工用!$B$1:$AP$47,ROW(),FALSE))</f>
         <v>0.71206143811477352</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDFBD76F-3256-4879-8F26-B76D5BC7766A}">
-  <dimension ref="A1:AO77"/>
+  <dimension ref="A1:AQ77"/>
   <sheetFormatPr defaultRowHeight="12.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.6640625" style="16" bestFit="1" customWidth="1"/>
@@ -7714,13 +7727,13 @@
     <col min="17" max="17" width="8.88671875" style="16"/>
     <col min="18" max="21" width="8.88671875" style="10"/>
     <col min="22" max="22" width="8.88671875" style="4"/>
-    <col min="28" max="36" width="8.88671875" style="10"/>
-    <col min="37" max="37" width="8.88671875" style="19"/>
-    <col min="38" max="39" width="8.88671875" style="10"/>
-    <col min="40" max="41" width="8.88671875" style="19"/>
+    <col min="28" max="38" width="8.88671875" style="10"/>
+    <col min="39" max="39" width="8.88671875" style="19"/>
+    <col min="40" max="41" width="8.88671875" style="10"/>
+    <col min="42" max="43" width="8.88671875" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -7818,34 +7831,40 @@
         <v>34</v>
       </c>
       <c r="AG1" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="AH1" s="8" t="s">
+      <c r="AJ1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="AI1" s="9" t="s">
+      <c r="AK1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="AJ1" s="9" t="s">
+      <c r="AL1" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="AK1" s="18" t="s">
+      <c r="AM1" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="AL1" s="9" t="s">
+      <c r="AN1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" s="9" t="s">
+      <c r="AO1" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" s="18" t="s">
+      <c r="AP1" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="19" t="s">
+      <c r="AQ1" s="19" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1995</v>
       </c>
@@ -7924,7 +7943,7 @@
         <v>210</v>
       </c>
       <c r="AB2" s="10">
-        <f>AC2/AF2*100</f>
+        <f>AC2/AH2*100</f>
         <v>93.293718166383712</v>
       </c>
       <c r="AC2" s="10">
@@ -7939,35 +7958,42 @@
       </c>
       <c r="AF2" s="10">
         <f>AG2</f>
+        <v>115.17469190537221</v>
+      </c>
+      <c r="AG2" s="10">
+        <v>115.17469190537221</v>
+      </c>
+      <c r="AH2" s="10">
+        <f>AI2</f>
         <v>117.8</v>
       </c>
-      <c r="AG2" s="10">
+      <c r="AI2" s="10">
         <v>117.8</v>
       </c>
-      <c r="AH2" s="10">
+      <c r="AJ2" s="10">
         <v>0.1</v>
       </c>
-      <c r="AI2" s="10">
+      <c r="AK2" s="10">
         <v>95.9</v>
       </c>
-      <c r="AK2" s="19">
+      <c r="AM2" s="19">
         <v>3.5058333333333298</v>
       </c>
-      <c r="AL2" s="10">
+      <c r="AN2" s="10">
         <v>136.375</v>
       </c>
-      <c r="AM2" s="10">
+      <c r="AO2" s="10">
         <v>77.849999999999994</v>
       </c>
-      <c r="AN2" s="19">
-        <f>AL2/AM2</f>
+      <c r="AP2" s="19">
+        <f>AN2/AO2</f>
         <v>1.7517662170841364</v>
       </c>
-      <c r="AO2" s="29">
+      <c r="AQ2" s="29">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1996</v>
       </c>
@@ -8054,7 +8080,7 @@
         <v>225</v>
       </c>
       <c r="AB3" s="10">
-        <f t="shared" ref="AB3:AB32" si="5">AC3/AF3*100</f>
+        <f t="shared" ref="AB3:AB32" si="5">AC3/AH3*100</f>
         <v>94.232400339270555</v>
       </c>
       <c r="AC3" s="10">
@@ -8068,40 +8094,47 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="AF3" s="10">
-        <f t="shared" ref="AF3:AF30" si="7">AG3</f>
+        <f t="shared" ref="AF3:AF47" si="7">AG3</f>
+        <v>115.41575265232549</v>
+      </c>
+      <c r="AG3" s="10">
+        <v>115.41575265232549</v>
+      </c>
+      <c r="AH3" s="10">
+        <f t="shared" ref="AH3:AH30" si="8">AI3</f>
         <v>117.9</v>
       </c>
-      <c r="AG3" s="10">
+      <c r="AI3" s="10">
         <v>117.9</v>
       </c>
-      <c r="AH3" s="10">
+      <c r="AJ3" s="10">
         <v>0.1</v>
       </c>
-      <c r="AI3" s="10">
+      <c r="AK3" s="10">
         <v>96</v>
       </c>
-      <c r="AJ3" s="10">
-        <f>(AI3/AI2-1)*100</f>
+      <c r="AL3" s="10">
+        <f>(AK3/AK2-1)*100</f>
         <v>0.10427528675702735</v>
       </c>
-      <c r="AK3" s="19">
+      <c r="AM3" s="19">
         <v>2.6575833333333301</v>
       </c>
-      <c r="AL3" s="10">
+      <c r="AN3" s="10">
         <v>129.71666666666701</v>
       </c>
-      <c r="AM3" s="10">
+      <c r="AO3" s="10">
         <v>85.408333333333303</v>
       </c>
-      <c r="AN3" s="19">
-        <f t="shared" ref="AN3:AN32" si="8">AL3/AM3</f>
+      <c r="AP3" s="19">
+        <f t="shared" ref="AP3:AP32" si="9">AN3/AO3</f>
         <v>1.5187823202263682</v>
       </c>
-      <c r="AO3" s="29">
+      <c r="AQ3" s="29">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1997</v>
       </c>
@@ -8113,7 +8146,7 @@
         <v>4.3922398281506378</v>
       </c>
       <c r="D4" s="21">
-        <f t="shared" ref="D4:D42" si="9">C4/C3</f>
+        <f t="shared" ref="D4:D42" si="10">C4/C3</f>
         <v>1.0120371232066527</v>
       </c>
       <c r="F4" s="16">
@@ -8156,7 +8189,7 @@
         <v>111.6</v>
       </c>
       <c r="R4" s="10">
-        <f t="shared" ref="R4:R32" si="10">(Q4/Q3-1)*100</f>
+        <f t="shared" ref="R4:R32" si="11">(Q4/Q3-1)*100</f>
         <v>8.9686098654695456E-2</v>
       </c>
       <c r="S4" s="10">
@@ -8203,39 +8236,46 @@
       </c>
       <c r="AF4" s="10">
         <f t="shared" si="7"/>
+        <v>113.73762097014865</v>
+      </c>
+      <c r="AG4" s="10">
+        <v>113.73762097014865</v>
+      </c>
+      <c r="AH4" s="10">
+        <f t="shared" si="8"/>
         <v>116.3</v>
       </c>
-      <c r="AG4" s="10">
+      <c r="AI4" s="10">
         <v>116.3</v>
       </c>
-      <c r="AH4" s="10">
+      <c r="AJ4" s="10">
         <v>-1.4</v>
       </c>
-      <c r="AI4" s="10">
+      <c r="AK4" s="10">
         <v>97.7</v>
       </c>
-      <c r="AJ4" s="10">
-        <f t="shared" ref="AJ4:AJ32" si="11">(AI4/AI3-1)*100</f>
+      <c r="AL4" s="10">
+        <f t="shared" ref="AL4:AL32" si="12">(AK4/AK3-1)*100</f>
         <v>1.7708333333333437</v>
       </c>
-      <c r="AK4" s="19">
+      <c r="AM4" s="19">
         <v>2.4488333333333299</v>
       </c>
-      <c r="AL4" s="10">
+      <c r="AN4" s="10">
         <v>123.908333333333</v>
       </c>
-      <c r="AM4" s="10">
+      <c r="AO4" s="10">
         <v>91.783333333333303</v>
       </c>
-      <c r="AN4" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP4" s="19">
+        <f t="shared" si="9"/>
         <v>1.3500090793535469</v>
       </c>
-      <c r="AO4" s="29">
+      <c r="AQ4" s="29">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1998</v>
       </c>
@@ -8247,7 +8287,7 @@
         <v>4.2958441394142577</v>
       </c>
       <c r="D5" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.97805318185984214</v>
       </c>
       <c r="F5" s="16">
@@ -8290,7 +8330,7 @@
         <v>111.4</v>
       </c>
       <c r="R5" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-0.17921146953403522</v>
       </c>
       <c r="S5" s="10">
@@ -8337,39 +8377,46 @@
       </c>
       <c r="AF5" s="10">
         <f t="shared" si="7"/>
+        <v>112.44018361662494</v>
+      </c>
+      <c r="AG5" s="10">
+        <v>112.44018361662494</v>
+      </c>
+      <c r="AH5" s="10">
+        <f t="shared" si="8"/>
         <v>115</v>
       </c>
-      <c r="AG5" s="10">
+      <c r="AI5" s="10">
         <v>115</v>
       </c>
-      <c r="AH5" s="10">
+      <c r="AJ5" s="10">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="AI5" s="10">
+      <c r="AK5" s="10">
         <v>98.3</v>
       </c>
-      <c r="AJ5" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL5" s="10">
+        <f t="shared" si="12"/>
         <v>0.61412487205732003</v>
       </c>
-      <c r="AK5" s="19">
+      <c r="AM5" s="19">
         <v>2.3209166666666698</v>
       </c>
-      <c r="AL5" s="10">
+      <c r="AN5" s="10">
         <v>119.375</v>
       </c>
-      <c r="AM5" s="10">
+      <c r="AO5" s="10">
         <v>87.325000000000003</v>
       </c>
-      <c r="AN5" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP5" s="19">
+        <f t="shared" si="9"/>
         <v>1.3670197537933009</v>
       </c>
-      <c r="AO5" s="29">
+      <c r="AQ5" s="29">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1999</v>
       </c>
@@ -8381,7 +8428,7 @@
         <v>4.216623903621306</v>
       </c>
       <c r="D6" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.98155886637829615</v>
       </c>
       <c r="F6" s="16">
@@ -8424,7 +8471,7 @@
         <v>109.9</v>
       </c>
       <c r="R6" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.3464991023339312</v>
       </c>
       <c r="S6" s="10">
@@ -8471,39 +8518,46 @@
       </c>
       <c r="AF6" s="10">
         <f t="shared" si="7"/>
+        <v>111.46218977563225</v>
+      </c>
+      <c r="AG6" s="10">
+        <v>111.46218977563225</v>
+      </c>
+      <c r="AH6" s="10">
+        <f t="shared" si="8"/>
         <v>113.7</v>
       </c>
-      <c r="AG6" s="10">
+      <c r="AI6" s="10">
         <v>113.7</v>
       </c>
-      <c r="AH6" s="10">
+      <c r="AJ6" s="10">
         <v>-1.2</v>
       </c>
-      <c r="AI6" s="10">
+      <c r="AK6" s="10">
         <v>98</v>
       </c>
-      <c r="AJ6" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL6" s="10">
+        <f t="shared" si="12"/>
         <v>-0.30518819938961661</v>
       </c>
-      <c r="AK6" s="19">
+      <c r="AM6" s="19">
         <v>2.1608333333333301</v>
       </c>
-      <c r="AL6" s="10">
+      <c r="AN6" s="10">
         <v>117.633333333333</v>
       </c>
-      <c r="AM6" s="10">
+      <c r="AO6" s="10">
         <v>79.2083333333333</v>
       </c>
-      <c r="AN6" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP6" s="19">
+        <f t="shared" si="9"/>
         <v>1.4851130983692757</v>
       </c>
-      <c r="AO6" s="29">
+      <c r="AQ6" s="29">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2000</v>
       </c>
@@ -8515,7 +8569,7 @@
         <v>4.2811937664465916</v>
       </c>
       <c r="D7" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0153131662441679</v>
       </c>
       <c r="F7" s="16">
@@ -8558,7 +8612,7 @@
         <v>108.6</v>
       </c>
       <c r="R7" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.1828935395814533</v>
       </c>
       <c r="S7" s="10">
@@ -8605,39 +8659,46 @@
       </c>
       <c r="AF7" s="10">
         <f t="shared" si="7"/>
+        <v>111.81760776843626</v>
+      </c>
+      <c r="AG7" s="10">
+        <v>111.81760776843626</v>
+      </c>
+      <c r="AH7" s="10">
+        <f t="shared" si="8"/>
         <v>114.5</v>
       </c>
-      <c r="AG7" s="10">
+      <c r="AI7" s="10">
         <v>114.5</v>
       </c>
-      <c r="AH7" s="10">
+      <c r="AJ7" s="10">
         <v>0.7</v>
       </c>
-      <c r="AI7" s="10">
+      <c r="AK7" s="10">
         <v>97.3</v>
       </c>
-      <c r="AJ7" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL7" s="10">
+        <f t="shared" si="12"/>
         <v>-0.71428571428571175</v>
       </c>
-      <c r="AK7" s="19">
+      <c r="AM7" s="19">
         <v>2.0671666666666701</v>
       </c>
-      <c r="AL7" s="10">
+      <c r="AN7" s="10">
         <v>118.72499999999999</v>
       </c>
-      <c r="AM7" s="10">
+      <c r="AO7" s="10">
         <v>82.9583333333333</v>
       </c>
-      <c r="AN7" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP7" s="19">
+        <f t="shared" si="9"/>
         <v>1.431140130587645</v>
       </c>
-      <c r="AO7" s="29">
+      <c r="AQ7" s="29">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2001</v>
       </c>
@@ -8649,7 +8710,7 @@
         <v>4.2370291243834242</v>
       </c>
       <c r="D8" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.98968403569833652</v>
       </c>
       <c r="F8" s="16">
@@ -8692,7 +8753,7 @@
         <v>107.5</v>
       </c>
       <c r="R8" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.012891344383049</v>
       </c>
       <c r="S8" s="10">
@@ -8739,39 +8800,46 @@
       </c>
       <c r="AF8" s="10">
         <f t="shared" si="7"/>
+        <v>110.92678083076923</v>
+      </c>
+      <c r="AG8" s="10">
+        <v>110.92678083076923</v>
+      </c>
+      <c r="AH8" s="10">
+        <f t="shared" si="8"/>
         <v>113.3</v>
       </c>
-      <c r="AG8" s="10">
+      <c r="AI8" s="10">
         <v>113.3</v>
       </c>
-      <c r="AH8" s="10">
+      <c r="AJ8" s="10">
         <v>-1</v>
       </c>
-      <c r="AI8" s="10">
+      <c r="AK8" s="10">
         <v>96.7</v>
       </c>
-      <c r="AJ8" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL8" s="10">
+        <f t="shared" si="12"/>
         <v>-0.61664953751283669</v>
       </c>
-      <c r="AK8" s="19">
+      <c r="AM8" s="19">
         <v>1.9694166666666699</v>
       </c>
-      <c r="AL8" s="10">
+      <c r="AN8" s="10">
         <v>113.1</v>
       </c>
-      <c r="AM8" s="10">
+      <c r="AO8" s="10">
         <v>84.983333333333306</v>
       </c>
-      <c r="AN8" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP8" s="19">
+        <f t="shared" si="9"/>
         <v>1.3308491861149248</v>
       </c>
-      <c r="AO8" s="29">
+      <c r="AQ8" s="29">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2002</v>
       </c>
@@ -8783,7 +8851,7 @@
         <v>4.1760726668026296</v>
       </c>
       <c r="D9" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.98561339660612668</v>
       </c>
       <c r="E9" s="16">
@@ -8829,7 +8897,7 @@
         <v>106</v>
       </c>
       <c r="R9" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.3953488372092981</v>
       </c>
       <c r="S9" s="10">
@@ -8876,39 +8944,46 @@
       </c>
       <c r="AF9" s="10">
         <f t="shared" si="7"/>
+        <v>110.15114467281128</v>
+      </c>
+      <c r="AG9" s="10">
+        <v>110.15114467281128</v>
+      </c>
+      <c r="AH9" s="10">
+        <f t="shared" si="8"/>
         <v>112.2</v>
       </c>
-      <c r="AG9" s="10">
+      <c r="AI9" s="10">
         <v>112.2</v>
       </c>
-      <c r="AH9" s="10">
+      <c r="AJ9" s="10">
         <v>-0.9</v>
       </c>
-      <c r="AI9" s="10">
+      <c r="AK9" s="10">
         <v>95.8</v>
       </c>
-      <c r="AJ9" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL9" s="10">
+        <f t="shared" si="12"/>
         <v>-0.93071354705274167</v>
       </c>
-      <c r="AK9" s="19">
+      <c r="AM9" s="19">
         <v>1.8649166666666701</v>
       </c>
-      <c r="AL9" s="10">
+      <c r="AN9" s="10">
         <v>108.783333333333</v>
       </c>
-      <c r="AM9" s="10">
+      <c r="AO9" s="10">
         <v>83.7916666666667</v>
       </c>
-      <c r="AN9" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP9" s="19">
+        <f t="shared" si="9"/>
         <v>1.2982595723520591</v>
       </c>
-      <c r="AO9" s="29">
+      <c r="AQ9" s="29">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2003</v>
       </c>
@@ -8920,7 +8995,7 @@
         <v>4.1522060551004749</v>
       </c>
       <c r="D10" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.99428491465393298</v>
       </c>
       <c r="E10" s="16">
@@ -8966,7 +9041,7 @@
         <v>104.1</v>
       </c>
       <c r="R10" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.7924528301886844</v>
       </c>
       <c r="S10" s="10">
@@ -9013,39 +9088,46 @@
       </c>
       <c r="AF10" s="10">
         <f t="shared" si="7"/>
+        <v>110.39588503769362</v>
+      </c>
+      <c r="AG10" s="10">
+        <v>110.39588503769362</v>
+      </c>
+      <c r="AH10" s="10">
+        <f t="shared" si="8"/>
         <v>112.2</v>
       </c>
-      <c r="AG10" s="10">
+      <c r="AI10" s="10">
         <v>112.2</v>
       </c>
-      <c r="AH10" s="10">
+      <c r="AJ10" s="10">
         <v>-0.1</v>
       </c>
-      <c r="AI10" s="10">
+      <c r="AK10" s="10">
         <v>95.5</v>
       </c>
-      <c r="AJ10" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL10" s="10">
+        <f t="shared" si="12"/>
         <v>-0.31315240083507057</v>
       </c>
-      <c r="AK10" s="19">
+      <c r="AM10" s="19">
         <v>1.8220833333333299</v>
       </c>
-      <c r="AL10" s="10">
+      <c r="AN10" s="10">
         <v>107.591666666667</v>
       </c>
-      <c r="AM10" s="10">
+      <c r="AO10" s="10">
         <v>83.05</v>
       </c>
-      <c r="AN10" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP10" s="19">
+        <f t="shared" si="9"/>
         <v>1.2955047160345214</v>
       </c>
-      <c r="AO10" s="29">
+      <c r="AQ10" s="29">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2004</v>
       </c>
@@ -9057,7 +9139,7 @@
         <v>4.1837909959542046</v>
       </c>
       <c r="D11" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0076067855098212</v>
       </c>
       <c r="E11" s="16">
@@ -9103,7 +9185,7 @@
         <v>102.8</v>
       </c>
       <c r="R11" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.2487992315081575</v>
       </c>
       <c r="S11" s="10">
@@ -9150,39 +9232,46 @@
       </c>
       <c r="AF11" s="10">
         <f t="shared" si="7"/>
+        <v>110.93583377116521</v>
+      </c>
+      <c r="AG11" s="10">
+        <v>110.93583377116521</v>
+      </c>
+      <c r="AH11" s="10">
+        <f t="shared" si="8"/>
         <v>112.4</v>
       </c>
-      <c r="AG11" s="10">
+      <c r="AI11" s="10">
         <v>112.4</v>
       </c>
-      <c r="AH11" s="10">
+      <c r="AJ11" s="10">
         <v>0.1</v>
       </c>
-      <c r="AI11" s="10">
+      <c r="AK11" s="10">
         <v>95.5</v>
       </c>
-      <c r="AJ11" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL11" s="10">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AK11" s="19">
+      <c r="AM11" s="19">
         <v>1.7665833333333301</v>
       </c>
-      <c r="AL11" s="10">
+      <c r="AN11" s="10">
         <v>109.8</v>
       </c>
-      <c r="AM11" s="10">
+      <c r="AO11" s="10">
         <v>86.525000000000006</v>
       </c>
-      <c r="AN11" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP11" s="19">
+        <f t="shared" si="9"/>
         <v>1.2689973995954926</v>
       </c>
-      <c r="AO11" s="29">
+      <c r="AQ11" s="29">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2005</v>
       </c>
@@ -9194,7 +9283,7 @@
         <v>4.2059451505854355</v>
       </c>
       <c r="D12" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0052952345498747</v>
       </c>
       <c r="E12" s="16">
@@ -9240,7 +9329,7 @@
         <v>101.5</v>
       </c>
       <c r="R12" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.2645914396887115</v>
       </c>
       <c r="S12" s="10">
@@ -9287,39 +9376,46 @@
       </c>
       <c r="AF12" s="10">
         <f t="shared" si="7"/>
+        <v>110.28131846733939</v>
+      </c>
+      <c r="AG12" s="10">
+        <v>110.28131846733939</v>
+      </c>
+      <c r="AH12" s="10">
+        <f t="shared" si="8"/>
         <v>111.7</v>
       </c>
-      <c r="AG12" s="10">
+      <c r="AI12" s="10">
         <v>111.7</v>
       </c>
-      <c r="AH12" s="10">
+      <c r="AJ12" s="10">
         <v>-0.6</v>
       </c>
-      <c r="AI12" s="10">
+      <c r="AK12" s="10">
         <v>95.2</v>
       </c>
-      <c r="AJ12" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL12" s="10">
+        <f t="shared" si="12"/>
         <v>-0.3141361256544517</v>
       </c>
-      <c r="AK12" s="19">
+      <c r="AM12" s="19">
         <v>1.6769166666666699</v>
       </c>
-      <c r="AL12" s="10">
+      <c r="AN12" s="10">
         <v>110.658333333333</v>
       </c>
-      <c r="AM12" s="10">
+      <c r="AO12" s="10">
         <v>97.841666666666697</v>
       </c>
-      <c r="AN12" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP12" s="19">
+        <f t="shared" si="9"/>
         <v>1.1309939528149184</v>
       </c>
-      <c r="AO12" s="29">
+      <c r="AQ12" s="29">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2006</v>
       </c>
@@ -9331,7 +9427,7 @@
         <v>4.2264407627774609</v>
       </c>
       <c r="D13" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0048730098606189</v>
       </c>
       <c r="E13" s="16">
@@ -9377,7 +9473,7 @@
         <v>100.5</v>
       </c>
       <c r="R13" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-0.98522167487684609</v>
       </c>
       <c r="S13" s="10">
@@ -9424,39 +9520,46 @@
       </c>
       <c r="AF13" s="10">
         <f t="shared" si="7"/>
+        <v>110.68616202764865</v>
+      </c>
+      <c r="AG13" s="10">
+        <v>110.68616202764865</v>
+      </c>
+      <c r="AH13" s="10">
+        <f t="shared" si="8"/>
         <v>112.2</v>
       </c>
-      <c r="AG13" s="10">
+      <c r="AI13" s="10">
         <v>112.2</v>
       </c>
-      <c r="AH13" s="10">
+      <c r="AJ13" s="10">
         <v>0.5</v>
       </c>
-      <c r="AI13" s="10">
+      <c r="AK13" s="10">
         <v>95.5</v>
       </c>
-      <c r="AJ13" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL13" s="10">
+        <f t="shared" si="12"/>
         <v>0.31512605042016695</v>
       </c>
-      <c r="AK13" s="19">
+      <c r="AM13" s="19">
         <v>1.6648333333333301</v>
       </c>
-      <c r="AL13" s="10">
+      <c r="AN13" s="10">
         <v>109.783333333333</v>
       </c>
-      <c r="AM13" s="10">
+      <c r="AO13" s="10">
         <v>111.45</v>
       </c>
-      <c r="AN13" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP13" s="19">
+        <f t="shared" si="9"/>
         <v>0.98504561088679232</v>
       </c>
-      <c r="AO13" s="29">
+      <c r="AQ13" s="29">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2007</v>
       </c>
@@ -9468,7 +9571,7 @@
         <v>4.2533651480477683</v>
       </c>
       <c r="D14" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0063704631820307</v>
       </c>
       <c r="E14" s="16">
@@ -9514,7 +9617,7 @@
         <v>99.5</v>
       </c>
       <c r="R14" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-0.99502487562188602</v>
       </c>
       <c r="S14" s="10">
@@ -9561,39 +9664,46 @@
       </c>
       <c r="AF14" s="10">
         <f t="shared" si="7"/>
+        <v>109.98496258143892</v>
+      </c>
+      <c r="AG14" s="10">
+        <v>109.98496258143892</v>
+      </c>
+      <c r="AH14" s="10">
+        <f t="shared" si="8"/>
         <v>111.4</v>
       </c>
-      <c r="AG14" s="10">
+      <c r="AI14" s="10">
         <v>111.4</v>
       </c>
-      <c r="AH14" s="10">
+      <c r="AJ14" s="10">
         <v>-0.8</v>
       </c>
-      <c r="AI14" s="10">
+      <c r="AK14" s="10">
         <v>95.5</v>
       </c>
-      <c r="AJ14" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL14" s="10">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AK14" s="19">
+      <c r="AM14" s="19">
         <v>1.8832500000000001</v>
       </c>
-      <c r="AL14" s="10">
+      <c r="AN14" s="10">
         <v>110.041666666667</v>
       </c>
-      <c r="AM14" s="10">
+      <c r="AO14" s="10">
         <v>119.841666666667</v>
       </c>
-      <c r="AN14" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP14" s="19">
+        <f t="shared" si="9"/>
         <v>0.91822543633961506</v>
       </c>
-      <c r="AO14" s="29">
+      <c r="AQ14" s="29">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2008</v>
       </c>
@@ -9605,7 +9715,7 @@
         <v>4.1641063676961991</v>
       </c>
       <c r="D15" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.97901455030435425</v>
       </c>
       <c r="E15" s="16">
@@ -9651,7 +9761,7 @@
         <v>98.6</v>
       </c>
       <c r="R15" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-0.90452261306532833</v>
       </c>
       <c r="S15" s="10">
@@ -9698,39 +9808,46 @@
       </c>
       <c r="AF15" s="10">
         <f t="shared" si="7"/>
+        <v>108.69178178681196</v>
+      </c>
+      <c r="AG15" s="10">
+        <v>108.69178178681196</v>
+      </c>
+      <c r="AH15" s="10">
+        <f t="shared" si="8"/>
         <v>110.2</v>
       </c>
-      <c r="AG15" s="10">
+      <c r="AI15" s="10">
         <v>110.2</v>
       </c>
-      <c r="AH15" s="10">
+      <c r="AJ15" s="10">
         <v>-1.2</v>
       </c>
-      <c r="AI15" s="10">
+      <c r="AK15" s="10">
         <v>96.8</v>
       </c>
-      <c r="AJ15" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL15" s="10">
+        <f t="shared" si="12"/>
         <v>1.3612565445026092</v>
       </c>
-      <c r="AK15" s="19">
+      <c r="AM15" s="19">
         <v>1.9095</v>
       </c>
-      <c r="AL15" s="10">
+      <c r="AN15" s="10">
         <v>112.325</v>
       </c>
-      <c r="AM15" s="10">
+      <c r="AO15" s="10">
         <v>130.15</v>
       </c>
-      <c r="AN15" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP15" s="19">
+        <f t="shared" si="9"/>
         <v>0.86304264310411061</v>
       </c>
-      <c r="AO15" s="29">
+      <c r="AQ15" s="29">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2009</v>
       </c>
@@ -9742,7 +9859,7 @@
         <v>3.9002882091977007</v>
       </c>
       <c r="D16" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.93664471192544096</v>
       </c>
       <c r="E16" s="16">
@@ -9788,7 +9905,7 @@
         <v>98.2</v>
       </c>
       <c r="R16" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-0.40567951318457585</v>
       </c>
       <c r="S16" s="10">
@@ -9835,39 +9952,46 @@
       </c>
       <c r="AF16" s="10">
         <f t="shared" si="7"/>
+        <v>105.72077611315964</v>
+      </c>
+      <c r="AG16" s="10">
+        <v>105.72077611315964</v>
+      </c>
+      <c r="AH16" s="10">
+        <f t="shared" si="8"/>
         <v>107</v>
       </c>
-      <c r="AG16" s="10">
+      <c r="AI16" s="10">
         <v>107</v>
       </c>
-      <c r="AH16" s="10">
+      <c r="AJ16" s="10">
         <v>-2.8</v>
       </c>
-      <c r="AI16" s="10">
+      <c r="AK16" s="10">
         <v>95.5</v>
       </c>
-      <c r="AJ16" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL16" s="10">
+        <f t="shared" si="12"/>
         <v>-1.342975206611563</v>
       </c>
-      <c r="AK16" s="19">
+      <c r="AM16" s="19">
         <v>1.7233333333333301</v>
       </c>
-      <c r="AL16" s="10">
+      <c r="AN16" s="10">
         <v>108.64166666666701</v>
       </c>
-      <c r="AM16" s="10">
+      <c r="AO16" s="10">
         <v>97.108333333333306</v>
       </c>
-      <c r="AN16" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP16" s="19">
+        <f t="shared" si="9"/>
         <v>1.1187676993049038</v>
       </c>
-      <c r="AO16" s="29">
+      <c r="AQ16" s="29">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2010</v>
       </c>
@@ -9879,7 +10003,7 @@
         <v>3.9836916373177567</v>
       </c>
       <c r="D17" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0213839141229033</v>
       </c>
       <c r="E17" s="16">
@@ -9925,7 +10049,7 @@
         <v>96.3</v>
       </c>
       <c r="R17" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.9348268839103899</v>
       </c>
       <c r="S17" s="10">
@@ -9972,39 +10096,46 @@
       </c>
       <c r="AF17" s="10">
         <f t="shared" si="7"/>
+        <v>106.88312336387678</v>
+      </c>
+      <c r="AG17" s="10">
+        <v>106.88312336387678</v>
+      </c>
+      <c r="AH17" s="10">
+        <f t="shared" si="8"/>
         <v>108.6</v>
       </c>
-      <c r="AG17" s="10">
+      <c r="AI17" s="10">
         <v>108.6</v>
       </c>
-      <c r="AH17" s="10">
+      <c r="AJ17" s="10">
         <v>1.5</v>
       </c>
-      <c r="AI17" s="10">
+      <c r="AK17" s="10">
         <v>94.8</v>
       </c>
-      <c r="AJ17" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL17" s="10">
+        <f t="shared" si="12"/>
         <v>-0.73298429319371694</v>
       </c>
-      <c r="AK17" s="19">
+      <c r="AM17" s="19">
         <v>1.5983333333333301</v>
       </c>
-      <c r="AL17" s="10">
+      <c r="AN17" s="10">
         <v>110.966666666667</v>
       </c>
-      <c r="AM17" s="10">
+      <c r="AO17" s="10">
         <v>104.008333333333</v>
       </c>
-      <c r="AN17" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP17" s="19">
+        <f t="shared" si="9"/>
         <v>1.0669016905696724</v>
       </c>
-      <c r="AO17" s="29">
+      <c r="AQ17" s="29">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2011</v>
       </c>
@@ -10016,7 +10147,7 @@
         <v>3.9202559569441622</v>
       </c>
       <c r="D18" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.98407615695468187</v>
       </c>
       <c r="E18" s="16">
@@ -10062,7 +10193,7 @@
         <v>94.8</v>
       </c>
       <c r="R18" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.5576323987538943</v>
       </c>
       <c r="S18" s="10">
@@ -10109,39 +10240,46 @@
       </c>
       <c r="AF18" s="10">
         <f t="shared" si="7"/>
+        <v>106.5405935511082</v>
+      </c>
+      <c r="AG18" s="10">
+        <v>106.5405935511082</v>
+      </c>
+      <c r="AH18" s="10">
+        <f t="shared" si="8"/>
         <v>108.3</v>
       </c>
-      <c r="AG18" s="10">
+      <c r="AI18" s="10">
         <v>108.3</v>
       </c>
-      <c r="AH18" s="10">
+      <c r="AJ18" s="10">
         <v>-0.3</v>
       </c>
-      <c r="AI18" s="10">
+      <c r="AK18" s="10">
         <v>94.5</v>
       </c>
-      <c r="AJ18" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL18" s="10">
+        <f t="shared" si="12"/>
         <v>-0.31645569620253333</v>
       </c>
-      <c r="AK18" s="19">
+      <c r="AM18" s="19">
         <v>1.50091666666667</v>
       </c>
-      <c r="AL18" s="10">
+      <c r="AN18" s="10">
         <v>114.416666666667</v>
       </c>
-      <c r="AM18" s="10">
+      <c r="AO18" s="10">
         <v>111.791666666667</v>
       </c>
-      <c r="AN18" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP18" s="19">
+        <f t="shared" si="9"/>
         <v>1.0234811777860604</v>
       </c>
-      <c r="AO18" s="29">
+      <c r="AQ18" s="29">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2012</v>
       </c>
@@ -10153,7 +10291,7 @@
         <v>3.9608528681040496</v>
       </c>
       <c r="D19" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0103556787122474</v>
       </c>
       <c r="E19" s="16">
@@ -10199,7 +10337,7 @@
         <v>94.1</v>
       </c>
       <c r="R19" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-0.73839662447258148</v>
       </c>
       <c r="S19" s="10">
@@ -10246,39 +10384,46 @@
       </c>
       <c r="AF19" s="10">
         <f t="shared" si="7"/>
+        <v>107.30591545242444</v>
+      </c>
+      <c r="AG19" s="10">
+        <v>107.30591545242444</v>
+      </c>
+      <c r="AH19" s="10">
+        <f t="shared" si="8"/>
         <v>108.9</v>
       </c>
-      <c r="AG19" s="10">
+      <c r="AI19" s="10">
         <v>108.9</v>
       </c>
-      <c r="AH19" s="10">
+      <c r="AJ19" s="10">
         <v>0.5</v>
       </c>
-      <c r="AI19" s="10">
+      <c r="AK19" s="10">
         <v>94.5</v>
       </c>
-      <c r="AJ19" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL19" s="10">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AK19" s="19">
+      <c r="AM19" s="19">
         <v>1.4075</v>
       </c>
-      <c r="AL19" s="10">
+      <c r="AN19" s="10">
         <v>112.75</v>
       </c>
-      <c r="AM19" s="10">
+      <c r="AO19" s="10">
         <v>111.558333333333</v>
       </c>
-      <c r="AN19" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP19" s="19">
+        <f t="shared" si="9"/>
         <v>1.0106820049301593</v>
       </c>
-      <c r="AO19" s="29">
+      <c r="AQ19" s="29">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2013</v>
       </c>
@@ -10290,7 +10435,7 @@
         <v>4.0384361216192879</v>
       </c>
       <c r="D20" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0195875121088189</v>
       </c>
       <c r="E20" s="16">
@@ -10336,7 +10481,7 @@
         <v>93.9</v>
       </c>
       <c r="R20" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-0.21253985122209329</v>
       </c>
       <c r="S20" s="10">
@@ -10383,39 +10528,46 @@
       </c>
       <c r="AF20" s="10">
         <f t="shared" si="7"/>
+        <v>106.20018909079735</v>
+      </c>
+      <c r="AG20" s="10">
+        <v>106.20018909079735</v>
+      </c>
+      <c r="AH20" s="10">
+        <f t="shared" si="8"/>
         <v>107.7</v>
       </c>
-      <c r="AG20" s="10">
+      <c r="AI20" s="10">
         <v>107.7</v>
       </c>
-      <c r="AH20" s="10">
+      <c r="AJ20" s="10">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="AI20" s="10">
+      <c r="AK20" s="10">
         <v>94.9</v>
       </c>
-      <c r="AJ20" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL20" s="10">
+        <f t="shared" si="12"/>
         <v>0.42328042328043658</v>
       </c>
-      <c r="AK20" s="19">
+      <c r="AM20" s="19">
         <v>1.30375</v>
       </c>
-      <c r="AL20" s="10">
+      <c r="AN20" s="10">
         <v>110.708333333333</v>
       </c>
-      <c r="AM20" s="10">
+      <c r="AO20" s="10">
         <v>127.708333333333</v>
       </c>
-      <c r="AN20" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP20" s="19">
+        <f t="shared" si="9"/>
         <v>0.86688417618270763</v>
       </c>
-      <c r="AO20" s="29">
+      <c r="AQ20" s="29">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2014</v>
       </c>
@@ -10427,7 +10579,7 @@
         <v>4.1514307945015991</v>
       </c>
       <c r="D21" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0279798093815098</v>
       </c>
       <c r="E21" s="16">
@@ -10473,7 +10625,7 @@
         <v>95.5</v>
       </c>
       <c r="R21" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.7039403620873195</v>
       </c>
       <c r="S21" s="10">
@@ -10520,39 +10672,46 @@
       </c>
       <c r="AF21" s="10">
         <f t="shared" si="7"/>
+        <v>105.96549576186771</v>
+      </c>
+      <c r="AG21" s="10">
+        <v>105.96549576186771</v>
+      </c>
+      <c r="AH21" s="10">
+        <f t="shared" si="8"/>
         <v>107.3</v>
       </c>
-      <c r="AG21" s="10">
+      <c r="AI21" s="10">
         <v>107.3</v>
       </c>
-      <c r="AH21" s="10">
+      <c r="AJ21" s="10">
         <v>-0.3</v>
       </c>
-      <c r="AI21" s="10">
+      <c r="AK21" s="10">
         <v>97.5</v>
       </c>
-      <c r="AJ21" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL21" s="10">
+        <f t="shared" si="12"/>
         <v>2.739726027397249</v>
       </c>
-      <c r="AK21" s="19">
+      <c r="AM21" s="19">
         <v>1.2191666666666701</v>
       </c>
-      <c r="AL21" s="10">
+      <c r="AN21" s="10">
         <v>108.708333333333</v>
       </c>
-      <c r="AM21" s="10">
+      <c r="AO21" s="10">
         <v>133.083333333333</v>
       </c>
-      <c r="AN21" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP21" s="19">
+        <f t="shared" si="9"/>
         <v>0.81684408265497765</v>
       </c>
-      <c r="AO21" s="29">
+      <c r="AQ21" s="29">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2015</v>
       </c>
@@ -10564,7 +10723,7 @@
         <v>4.3185546244934887</v>
       </c>
       <c r="D22" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0402569230380134</v>
       </c>
       <c r="E22" s="16">
@@ -10610,7 +10769,7 @@
         <v>97.5</v>
       </c>
       <c r="R22" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.0942408376963373</v>
       </c>
       <c r="S22" s="10">
@@ -10657,39 +10816,46 @@
       </c>
       <c r="AF22" s="10">
         <f t="shared" si="7"/>
+        <v>105.54785363345115</v>
+      </c>
+      <c r="AG22" s="10">
+        <v>105.54785363345115</v>
+      </c>
+      <c r="AH22" s="10">
+        <f t="shared" si="8"/>
         <v>106.9</v>
       </c>
-      <c r="AG22" s="10">
+      <c r="AI22" s="10">
         <v>106.9</v>
       </c>
-      <c r="AH22" s="10">
+      <c r="AJ22" s="10">
         <v>-0.3</v>
       </c>
-      <c r="AI22" s="10">
+      <c r="AK22" s="10">
         <v>98.2</v>
       </c>
-      <c r="AJ22" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL22" s="10">
+        <f t="shared" si="12"/>
         <v>0.71794871794872428</v>
       </c>
-      <c r="AK22" s="19">
+      <c r="AM22" s="19">
         <v>1.14283333333333</v>
       </c>
-      <c r="AL22" s="10">
+      <c r="AN22" s="10">
         <v>102.64166666666701</v>
       </c>
-      <c r="AM22" s="10">
+      <c r="AO22" s="10">
         <v>118.116666666667</v>
       </c>
-      <c r="AN22" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP22" s="19">
+        <f t="shared" si="9"/>
         <v>0.8689854663468326</v>
       </c>
-      <c r="AO22" s="29">
+      <c r="AQ22" s="29">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2016</v>
       </c>
@@ -10701,7 +10867,7 @@
         <v>4.3762739881299098</v>
       </c>
       <c r="D23" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0133654355809361</v>
       </c>
       <c r="E23" s="16">
@@ -10747,7 +10913,7 @@
         <v>98.1</v>
       </c>
       <c r="R23" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.61538461538461764</v>
       </c>
       <c r="S23" s="10">
@@ -10794,39 +10960,46 @@
       </c>
       <c r="AF23" s="10">
         <f t="shared" si="7"/>
+        <v>105.10387255783979</v>
+      </c>
+      <c r="AG23" s="10">
+        <v>105.10387255783979</v>
+      </c>
+      <c r="AH23" s="10">
+        <f t="shared" si="8"/>
         <v>106.3</v>
       </c>
-      <c r="AG23" s="10">
+      <c r="AI23" s="10">
         <v>106.3</v>
       </c>
-      <c r="AH23" s="10">
+      <c r="AJ23" s="10">
         <v>-0.6</v>
       </c>
-      <c r="AI23" s="10">
+      <c r="AK23" s="10">
         <v>98.1</v>
       </c>
-      <c r="AJ23" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL23" s="10">
+        <f t="shared" si="12"/>
         <v>-0.10183299389002753</v>
       </c>
-      <c r="AK23" s="19">
+      <c r="AM23" s="19">
         <v>1.0447500000000001</v>
       </c>
-      <c r="AL23" s="10">
+      <c r="AN23" s="10">
         <v>99.424999999999997</v>
       </c>
-      <c r="AM23" s="10">
+      <c r="AO23" s="10">
         <v>98.7083333333333</v>
       </c>
-      <c r="AN23" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP23" s="19">
+        <f t="shared" si="9"/>
         <v>1.0072604474461802</v>
       </c>
-      <c r="AO23" s="29">
+      <c r="AQ23" s="29">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2017</v>
       </c>
@@ -10838,7 +11011,7 @@
         <v>4.4525957500453046</v>
       </c>
       <c r="D24" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0174398957017792</v>
       </c>
       <c r="E24" s="16">
@@ -10884,7 +11057,7 @@
         <v>98.1</v>
       </c>
       <c r="R24" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="S24" s="10">
@@ -10931,39 +11104,46 @@
       </c>
       <c r="AF24" s="10">
         <f t="shared" si="7"/>
+        <v>105.17208576035692</v>
+      </c>
+      <c r="AG24" s="10">
+        <v>105.17208576035692</v>
+      </c>
+      <c r="AH24" s="10">
+        <f t="shared" si="8"/>
         <v>106.1</v>
       </c>
-      <c r="AG24" s="10">
+      <c r="AI24" s="10">
         <v>106.1</v>
       </c>
-      <c r="AH24" s="10">
+      <c r="AJ24" s="10">
         <v>-0.2</v>
       </c>
-      <c r="AI24" s="10">
+      <c r="AK24" s="10">
         <v>98.6</v>
       </c>
-      <c r="AJ24" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL24" s="10">
+        <f t="shared" si="12"/>
         <v>0.50968399592252744</v>
       </c>
-      <c r="AK24" s="19">
+      <c r="AM24" s="19">
         <v>0.96941666666666704</v>
       </c>
-      <c r="AL24" s="10">
+      <c r="AN24" s="10">
         <v>102.791666666667</v>
       </c>
-      <c r="AM24" s="10">
+      <c r="AO24" s="10">
         <v>109.52500000000001</v>
       </c>
-      <c r="AN24" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP24" s="19">
+        <f t="shared" si="9"/>
         <v>0.93852240736514037</v>
       </c>
-      <c r="AO24" s="29">
+      <c r="AQ24" s="29">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2018</v>
       </c>
@@ -10975,7 +11155,7 @@
         <v>4.4903983463380381</v>
       </c>
       <c r="D25" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0084900131102961</v>
       </c>
       <c r="E25" s="16">
@@ -11021,7 +11201,7 @@
         <v>98</v>
       </c>
       <c r="R25" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-0.10193679918449883</v>
       </c>
       <c r="S25" s="10">
@@ -11068,39 +11248,46 @@
       </c>
       <c r="AF25" s="10">
         <f t="shared" si="7"/>
+        <v>104.11521257191903</v>
+      </c>
+      <c r="AG25" s="10">
+        <v>104.11521257191903</v>
+      </c>
+      <c r="AH25" s="10">
+        <f t="shared" si="8"/>
         <v>105.2</v>
       </c>
-      <c r="AG25" s="10">
+      <c r="AI25" s="10">
         <v>105.2</v>
       </c>
-      <c r="AH25" s="10">
+      <c r="AJ25" s="10">
         <v>-0.8</v>
       </c>
-      <c r="AI25" s="10">
+      <c r="AK25" s="10">
         <v>99.5</v>
       </c>
-      <c r="AJ25" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL25" s="10">
+        <f t="shared" si="12"/>
         <v>0.91277890466532341</v>
       </c>
-      <c r="AK25" s="19">
+      <c r="AM25" s="19">
         <v>0.92174999999999996</v>
       </c>
-      <c r="AL25" s="10">
+      <c r="AN25" s="10">
         <v>104.916666666667</v>
       </c>
-      <c r="AM25" s="10">
+      <c r="AO25" s="10">
         <v>117.758333333333</v>
       </c>
-      <c r="AN25" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP25" s="19">
+        <f t="shared" si="9"/>
         <v>0.8909489774255237</v>
       </c>
-      <c r="AO25" s="29">
+      <c r="AQ25" s="29">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2019</v>
       </c>
@@ -11112,7 +11299,7 @@
         <v>4.5184939354430878</v>
       </c>
       <c r="D26" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0062568144155768</v>
       </c>
       <c r="E26" s="16">
@@ -11158,7 +11345,7 @@
         <v>98.7</v>
       </c>
       <c r="R26" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.71428571428571175</v>
       </c>
       <c r="S26" s="10">
@@ -11205,39 +11392,46 @@
       </c>
       <c r="AF26" s="10">
         <f t="shared" si="7"/>
+        <v>102.25995145350291</v>
+      </c>
+      <c r="AG26" s="10">
+        <v>102.25995145350291</v>
+      </c>
+      <c r="AH26" s="10">
+        <f t="shared" si="8"/>
         <v>102.9</v>
       </c>
-      <c r="AG26" s="10">
+      <c r="AI26" s="10">
         <v>102.9</v>
       </c>
-      <c r="AH26" s="10">
+      <c r="AJ26" s="10">
         <v>-2.2000000000000002</v>
       </c>
-      <c r="AI26" s="10">
+      <c r="AK26" s="10">
         <v>100</v>
       </c>
-      <c r="AJ26" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL26" s="10">
+        <f t="shared" si="12"/>
         <v>0.50251256281406143</v>
       </c>
-      <c r="AK26" s="19">
+      <c r="AM26" s="19">
         <v>0.88100000000000001</v>
       </c>
-      <c r="AL26" s="10">
+      <c r="AN26" s="10">
         <v>102.091666666667</v>
       </c>
-      <c r="AM26" s="10">
+      <c r="AO26" s="10">
         <v>111.533333333333</v>
       </c>
-      <c r="AN26" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP26" s="19">
+        <f t="shared" si="9"/>
         <v>0.91534668260610252</v>
       </c>
-      <c r="AO26" s="29">
+      <c r="AQ26" s="29">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2020</v>
       </c>
@@ -11249,7 +11443,7 @@
         <v>4.3923263520048197</v>
       </c>
       <c r="D27" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.97207751404763232</v>
       </c>
       <c r="E27" s="16">
@@ -11295,7 +11489,7 @@
         <v>100</v>
       </c>
       <c r="R27" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.3171225937183451</v>
       </c>
       <c r="S27" s="10">
@@ -11348,33 +11542,40 @@
         <v>100</v>
       </c>
       <c r="AH27" s="10">
-        <v>-2.8</v>
+        <f t="shared" si="8"/>
+        <v>100</v>
       </c>
       <c r="AI27" s="10">
         <v>100</v>
       </c>
       <c r="AJ27" s="10">
-        <f t="shared" si="11"/>
+        <v>-2.8</v>
+      </c>
+      <c r="AK27" s="10">
+        <v>100</v>
+      </c>
+      <c r="AL27" s="10">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AK27" s="19">
+      <c r="AM27" s="19">
         <v>0.82666666666666699</v>
       </c>
-      <c r="AL27" s="10">
+      <c r="AN27" s="10">
         <v>100</v>
       </c>
-      <c r="AM27" s="10">
+      <c r="AO27" s="10">
         <v>100.008333333333</v>
       </c>
-      <c r="AN27" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP27" s="19">
+        <f t="shared" si="9"/>
         <v>0.99991667361053582</v>
       </c>
-      <c r="AO27" s="29">
+      <c r="AQ27" s="29">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2021</v>
       </c>
@@ -11386,7 +11587,7 @@
         <v>4.5692862890055528</v>
       </c>
       <c r="D28" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0402884309632325</v>
       </c>
       <c r="E28" s="16">
@@ -11432,7 +11633,7 @@
         <v>99.9</v>
       </c>
       <c r="R28" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-9.9999999999988987E-2</v>
       </c>
       <c r="S28" s="10">
@@ -11479,39 +11680,46 @@
       </c>
       <c r="AF28" s="10">
         <f t="shared" si="7"/>
+        <v>101.15693191092603</v>
+      </c>
+      <c r="AG28" s="10">
+        <v>101.15693191092603</v>
+      </c>
+      <c r="AH28" s="10">
+        <f t="shared" si="8"/>
         <v>100.7</v>
       </c>
-      <c r="AG28" s="10">
+      <c r="AI28" s="10">
         <v>100.7</v>
       </c>
-      <c r="AH28" s="10">
+      <c r="AJ28" s="10">
         <v>0.6</v>
       </c>
-      <c r="AI28" s="10">
+      <c r="AK28" s="10">
         <v>99.8</v>
       </c>
-      <c r="AJ28" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL28" s="10">
+        <f t="shared" si="12"/>
         <v>-0.20000000000000018</v>
       </c>
-      <c r="AK28" s="19">
+      <c r="AM28" s="19">
         <v>0.80408333333333304</v>
       </c>
-      <c r="AL28" s="10">
+      <c r="AN28" s="10">
         <v>105.783333333333</v>
       </c>
-      <c r="AM28" s="10">
+      <c r="AO28" s="10">
         <v>121.575</v>
       </c>
-      <c r="AN28" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP28" s="19">
+        <f t="shared" si="9"/>
         <v>0.87010761532661318</v>
       </c>
-      <c r="AO28" s="29">
+      <c r="AQ28" s="29">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2022</v>
       </c>
@@ -11523,7 +11731,7 @@
         <v>4.680028485013362</v>
       </c>
       <c r="D29" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0242362130546017</v>
       </c>
       <c r="E29" s="16">
@@ -11569,7 +11777,7 @@
         <v>100.6</v>
       </c>
       <c r="R29" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.70070070070069601</v>
       </c>
       <c r="S29" s="10">
@@ -11616,39 +11824,46 @@
       </c>
       <c r="AF29" s="10">
         <f t="shared" si="7"/>
+        <v>100.97772178061501</v>
+      </c>
+      <c r="AG29" s="10">
+        <v>100.97772178061501</v>
+      </c>
+      <c r="AH29" s="10">
+        <f t="shared" si="8"/>
         <v>100.8</v>
       </c>
-      <c r="AG29" s="10">
+      <c r="AI29" s="10">
         <v>100.8</v>
       </c>
-      <c r="AH29" s="10">
+      <c r="AJ29" s="10">
         <v>0.1</v>
       </c>
-      <c r="AI29" s="10">
+      <c r="AK29" s="10">
         <v>102.3</v>
       </c>
-      <c r="AJ29" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL29" s="10">
+        <f t="shared" si="12"/>
         <v>2.5050100200400882</v>
       </c>
-      <c r="AK29" s="19">
+      <c r="AM29" s="19">
         <v>0.78349999999999997</v>
       </c>
-      <c r="AL29" s="10">
+      <c r="AN29" s="10">
         <v>110.741666666667</v>
       </c>
-      <c r="AM29" s="10">
+      <c r="AO29" s="10">
         <v>169.09166666666701</v>
       </c>
-      <c r="AN29" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP29" s="19">
+        <f t="shared" si="9"/>
         <v>0.65492090089202171</v>
       </c>
-      <c r="AO29" s="29">
+      <c r="AQ29" s="29">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2023</v>
       </c>
@@ -11660,7 +11875,7 @@
         <v>4.9517153237733904</v>
       </c>
       <c r="D30" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0580523899865222</v>
       </c>
       <c r="E30" s="16">
@@ -11706,7 +11921,7 @@
         <v>105.1</v>
       </c>
       <c r="R30" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.4731610337972239</v>
       </c>
       <c r="S30" s="10">
@@ -11751,41 +11966,48 @@
       <c r="AE30" s="12">
         <v>1.2</v>
       </c>
-      <c r="AF30" s="28">
+      <c r="AF30" s="30">
         <f t="shared" si="7"/>
+        <v>101.10061589869525</v>
+      </c>
+      <c r="AG30" s="30">
+        <v>101.10061589869525</v>
+      </c>
+      <c r="AH30" s="28">
+        <f t="shared" si="8"/>
         <v>100.9</v>
       </c>
-      <c r="AG30" s="28">
+      <c r="AI30" s="28">
         <v>100.9</v>
       </c>
-      <c r="AH30" s="28">
+      <c r="AJ30" s="28">
         <v>0.1</v>
       </c>
-      <c r="AI30" s="10">
+      <c r="AK30" s="10">
         <v>105.6</v>
       </c>
-      <c r="AJ30" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL30" s="10">
+        <f t="shared" si="12"/>
         <v>3.2258064516129004</v>
       </c>
-      <c r="AK30" s="19">
+      <c r="AM30" s="19">
         <v>0.77691666666666703</v>
       </c>
-      <c r="AL30" s="10">
+      <c r="AN30" s="10">
         <v>110.508333333333</v>
       </c>
-      <c r="AM30" s="10">
+      <c r="AO30" s="10">
         <v>161.208333333333</v>
       </c>
-      <c r="AN30" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP30" s="19">
+        <f t="shared" si="9"/>
         <v>0.68550012923235915</v>
       </c>
-      <c r="AO30" s="29">
+      <c r="AQ30" s="29">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2024</v>
       </c>
@@ -11797,7 +12019,7 @@
         <v>5.1211685669067535</v>
       </c>
       <c r="D31" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0342211197642586</v>
       </c>
       <c r="E31" s="16">
@@ -11843,7 +12065,7 @@
         <v>108.5</v>
       </c>
       <c r="R31" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.2350142721217834</v>
       </c>
       <c r="S31" s="10">
@@ -11888,41 +12110,48 @@
       <c r="AE31" s="11">
         <v>2.8</v>
       </c>
-      <c r="AF31" s="10">
-        <f>AF30*(1+AH31/100)</f>
+      <c r="AF31" s="31">
+        <f t="shared" si="7"/>
+        <v>100.15188070898171</v>
+      </c>
+      <c r="AG31" s="31">
+        <v>100.15188070898171</v>
+      </c>
+      <c r="AH31" s="9">
+        <f>AH30*(1+AJ31/100)</f>
         <v>99.891000000000005</v>
       </c>
-      <c r="AG31" s="10">
+      <c r="AI31" s="10">
         <v>101.4</v>
       </c>
-      <c r="AH31" s="11">
+      <c r="AJ31" s="31">
         <v>-1</v>
       </c>
-      <c r="AI31" s="10">
+      <c r="AK31" s="10">
         <v>108.5</v>
       </c>
-      <c r="AJ31" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL31" s="10">
+        <f t="shared" si="12"/>
         <v>2.7462121212121327</v>
       </c>
-      <c r="AK31" s="19">
+      <c r="AM31" s="19">
         <v>0.84183333333333299</v>
       </c>
-      <c r="AL31" s="10">
+      <c r="AN31" s="10">
         <v>112.6</v>
       </c>
-      <c r="AM31" s="10">
+      <c r="AO31" s="10">
         <v>165.541666666667</v>
       </c>
-      <c r="AN31" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP31" s="19">
+        <f t="shared" si="9"/>
         <v>0.68019129121570465</v>
       </c>
-      <c r="AO31" s="29">
+      <c r="AQ31" s="29">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2025</v>
       </c>
@@ -11934,7 +12163,7 @@
         <v>5.3849304733007743</v>
       </c>
       <c r="D32" s="22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.051504242234568</v>
       </c>
       <c r="E32" s="16">
@@ -11974,14 +12203,14 @@
         <v>151540.05198156688</v>
       </c>
       <c r="P32" s="17">
-        <f>P31*(AI32/AI31)</f>
+        <f>P31*(AK32/AK31)</f>
         <v>512217.24801843317</v>
       </c>
       <c r="Q32" s="16">
         <v>112.2</v>
       </c>
       <c r="R32" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.410138248847927</v>
       </c>
       <c r="S32" s="10">
@@ -12026,41 +12255,49 @@
       <c r="AE32" s="11">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AF32" s="10">
-        <f>AF31*(1+AH32/100)</f>
+      <c r="AF32" s="31">
+        <f t="shared" si="7"/>
+        <v>98.749754379055958</v>
+      </c>
+      <c r="AG32" s="9">
+        <f>AG31*(1+AJ32/100)</f>
+        <v>98.749754379055958</v>
+      </c>
+      <c r="AH32" s="9">
+        <f>AH31*(1+AJ32/100)</f>
         <v>98.492525999999998</v>
       </c>
-      <c r="AG32" s="10">
+      <c r="AI32" s="10">
         <v>100</v>
       </c>
-      <c r="AH32" s="11">
+      <c r="AJ32" s="31">
         <v>-1.4</v>
       </c>
-      <c r="AI32" s="10">
+      <c r="AK32" s="10">
         <v>111.9</v>
       </c>
-      <c r="AJ32" s="10">
-        <f t="shared" si="11"/>
+      <c r="AL32" s="10">
+        <f t="shared" si="12"/>
         <v>3.133640552995387</v>
       </c>
-      <c r="AK32" s="19">
+      <c r="AM32" s="19">
         <v>1.1034999999999999</v>
       </c>
-      <c r="AL32" s="10">
+      <c r="AN32" s="10">
         <v>112.808333333333</v>
       </c>
-      <c r="AM32" s="10">
+      <c r="AO32" s="10">
         <v>158.42500000000001</v>
       </c>
-      <c r="AN32" s="19">
-        <f t="shared" si="8"/>
+      <c r="AP32" s="19">
+        <f t="shared" si="9"/>
         <v>0.71206143811477352</v>
       </c>
-      <c r="AO32" s="29">
+      <c r="AQ32" s="29">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2026</v>
       </c>
@@ -12073,7 +12310,7 @@
         <v>5.5952996323199722</v>
       </c>
       <c r="D33" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0390662720832213</v>
       </c>
       <c r="E33" s="16">
@@ -12115,31 +12352,43 @@
       <c r="X33" s="4">
         <v>13355</v>
       </c>
-      <c r="AF33" s="11">
-        <f>_xlfn.FORECAST.LINEAR($AO33,AF2:AF32,$AO2:$AO32)</f>
+      <c r="AF33" s="10">
+        <f t="shared" si="7"/>
+        <v>99.282354561790484</v>
+      </c>
+      <c r="AG33" s="11">
+        <f t="shared" ref="AG33:AG47" si="13">AG32*(1+AJ33/100)</f>
+        <v>99.282354561790484</v>
+      </c>
+      <c r="AH33" s="11">
+        <f>_xlfn.FORECAST.LINEAR($AQ33,AH2:AH32,$AQ2:$AQ32)</f>
         <v>99.023738838709704</v>
       </c>
-      <c r="AI33" s="11">
-        <f>AI32*(1+AJ33/100)</f>
+      <c r="AJ33" s="11">
+        <f>AH33/AH32*100-100</f>
+        <v>0.53934329870848785</v>
+      </c>
+      <c r="AK33" s="11">
+        <f>AK32*(1+AL33/100)</f>
         <v>114.0261</v>
       </c>
-      <c r="AJ33" s="11">
+      <c r="AL33" s="11">
         <v>1.9</v>
       </c>
-      <c r="AN33" s="27">
-        <f>AN32</f>
+      <c r="AP33" s="27">
+        <f>AP32</f>
         <v>0.71206143811477352</v>
       </c>
-      <c r="AO33" s="29">
+      <c r="AQ33" s="29">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2027</v>
       </c>
       <c r="B34" s="16">
-        <f t="shared" ref="B34:B42" si="12">B33*(1+E34/100)</f>
+        <f t="shared" ref="B34:B42" si="14">B33*(1+E34/100)</f>
         <v>697306.24897120008</v>
       </c>
       <c r="C34" s="16">
@@ -12147,36 +12396,36 @@
         <v>5.7135643617973848</v>
       </c>
       <c r="D34" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.021136442594474</v>
       </c>
       <c r="E34" s="16">
         <v>1.6</v>
       </c>
       <c r="F34" s="17">
-        <f t="shared" ref="F34:F47" si="13">F33*(1+$E34/100)</f>
+        <f t="shared" ref="F34:F47" si="15">F33*(1+$E34/100)</f>
         <v>369358.663872</v>
       </c>
       <c r="G34" s="17">
-        <f t="shared" ref="G34:G47" si="14">G33*(1+$E34/100)</f>
+        <f t="shared" ref="G34:G47" si="16">G33*(1+$E34/100)</f>
         <v>159251.96496000001</v>
       </c>
       <c r="Q34" s="17">
-        <f t="shared" ref="Q34:Q47" si="15">Q33*(1+R34/100)</f>
+        <f t="shared" ref="Q34:Q47" si="17">Q33*(1+R34/100)</f>
         <v>115.702884</v>
       </c>
       <c r="R34" s="11">
         <v>1.1000000000000001</v>
       </c>
       <c r="S34" s="11">
-        <f t="shared" ref="S34:S47" si="16">S33*(1+R34/100)</f>
+        <f t="shared" ref="S34:S47" si="18">S33*(1+R34/100)</f>
         <v>117.455958</v>
       </c>
       <c r="T34" s="11">
         <v>0.7</v>
       </c>
       <c r="U34" s="11">
-        <f t="shared" ref="U34:U47" si="17">U33</f>
+        <f t="shared" ref="U34:U47" si="19">U33</f>
         <v>0.3</v>
       </c>
       <c r="V34" s="4">
@@ -12189,31 +12438,43 @@
       <c r="X34" s="4">
         <v>13100</v>
       </c>
-      <c r="AF34" s="11">
-        <f t="shared" ref="AF34:AF47" si="18">_xlfn.FORECAST.LINEAR(AO34,AF3:AF33,AO3:AO33)</f>
+      <c r="AF34" s="10">
+        <f t="shared" si="7"/>
+        <v>98.696902131184189</v>
+      </c>
+      <c r="AG34" s="11">
+        <f t="shared" si="13"/>
+        <v>98.696902131184189</v>
+      </c>
+      <c r="AH34" s="11">
+        <f t="shared" ref="AH34:AH47" si="20">_xlfn.FORECAST.LINEAR(AQ34,AH3:AH33,AQ3:AQ33)</f>
         <v>98.439811424349642</v>
       </c>
-      <c r="AI34" s="11">
-        <f t="shared" ref="AI34:AI47" si="19">AI33*(1+AJ34/100)</f>
+      <c r="AJ34" s="11">
+        <f t="shared" ref="AJ34:AJ47" si="21">AH34/AH33*100-100</f>
+        <v>-0.58968427289053693</v>
+      </c>
+      <c r="AK34" s="11">
+        <f t="shared" ref="AK34:AK47" si="22">AK33*(1+AL34/100)</f>
         <v>115.6224654</v>
       </c>
-      <c r="AJ34" s="11">
+      <c r="AL34" s="11">
         <v>1.4</v>
       </c>
-      <c r="AN34" s="27">
-        <f t="shared" ref="AN34:AN47" si="20">AN33</f>
+      <c r="AP34" s="27">
+        <f t="shared" ref="AP34:AP47" si="23">AP33</f>
         <v>0.71206143811477352</v>
       </c>
-      <c r="AO34" s="29">
+      <c r="AQ34" s="29">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2028</v>
       </c>
       <c r="B35" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>705673.92395885452</v>
       </c>
       <c r="C35" s="16">
@@ -12221,36 +12482,36 @@
         <v>5.8121297705277355</v>
       </c>
       <c r="D35" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0172511242525575</v>
       </c>
       <c r="E35" s="16">
         <v>1.2</v>
       </c>
       <c r="F35" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>373790.96783846401</v>
       </c>
       <c r="G35" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>161162.98853952001</v>
       </c>
       <c r="Q35" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>116.51280418799999</v>
       </c>
       <c r="R35" s="11">
         <v>0.7</v>
       </c>
       <c r="S35" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>118.27814970599998</v>
       </c>
       <c r="T35" s="11">
         <v>0.6</v>
       </c>
       <c r="U35" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.3</v>
       </c>
       <c r="V35" s="4">
@@ -12263,31 +12524,43 @@
       <c r="X35" s="4">
         <v>12850</v>
       </c>
-      <c r="AF35" s="11">
-        <f t="shared" si="18"/>
+      <c r="AF35" s="10">
+        <f t="shared" si="7"/>
+        <v>98.164476297106987</v>
+      </c>
+      <c r="AG35" s="11">
+        <f t="shared" si="13"/>
+        <v>98.164476297106987</v>
+      </c>
+      <c r="AH35" s="11">
+        <f t="shared" si="20"/>
         <v>97.908772480145018</v>
       </c>
-      <c r="AI35" s="11">
-        <f t="shared" si="19"/>
+      <c r="AJ35" s="11">
+        <f t="shared" si="21"/>
+        <v>-0.53945546676786194</v>
+      </c>
+      <c r="AK35" s="11">
+        <f t="shared" si="22"/>
         <v>116.89431251939999</v>
       </c>
-      <c r="AJ35" s="11">
+      <c r="AL35" s="11">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AN35" s="27">
-        <f t="shared" si="20"/>
+      <c r="AP35" s="27">
+        <f t="shared" si="23"/>
         <v>0.71206143811477352</v>
       </c>
-      <c r="AO35" s="29">
+      <c r="AQ35" s="29">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2029</v>
       </c>
       <c r="B36" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>714142.01104636083</v>
       </c>
       <c r="C36" s="16">
@@ -12295,36 +12568,36 @@
         <v>5.9131911721055621</v>
       </c>
       <c r="D36" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0173880153348074</v>
       </c>
       <c r="E36" s="16">
         <v>1.2</v>
       </c>
       <c r="F36" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>378276.4594525256</v>
       </c>
       <c r="G36" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>163096.94440199426</v>
       </c>
       <c r="Q36" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>117.32839381731598</v>
       </c>
       <c r="R36" s="11">
         <v>0.7</v>
       </c>
       <c r="S36" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>119.10609675394197</v>
       </c>
       <c r="T36" s="11">
         <v>0.6</v>
       </c>
       <c r="U36" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.3</v>
       </c>
       <c r="V36" s="4">
@@ -12337,31 +12610,43 @@
       <c r="X36" s="4">
         <v>12625</v>
       </c>
-      <c r="AF36" s="11">
-        <f t="shared" si="18"/>
+      <c r="AF36" s="10">
+        <f t="shared" si="7"/>
+        <v>97.575382915046902</v>
+      </c>
+      <c r="AG36" s="11">
+        <f t="shared" si="13"/>
+        <v>97.575382915046902</v>
+      </c>
+      <c r="AH36" s="11">
+        <f t="shared" si="20"/>
         <v>97.321213598466571</v>
       </c>
-      <c r="AI36" s="11">
-        <f t="shared" si="19"/>
+      <c r="AJ36" s="11">
+        <f t="shared" si="21"/>
+        <v>-0.60010851611647809</v>
+      </c>
+      <c r="AK36" s="11">
+        <f t="shared" si="22"/>
         <v>118.18014995711337</v>
       </c>
-      <c r="AJ36" s="11">
+      <c r="AL36" s="11">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AN36" s="27">
-        <f t="shared" si="20"/>
+      <c r="AP36" s="27">
+        <f t="shared" si="23"/>
         <v>0.71206143811477352</v>
       </c>
-      <c r="AO36" s="29">
+      <c r="AQ36" s="29">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2030</v>
       </c>
       <c r="B37" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>722711.71517891716</v>
       </c>
       <c r="C37" s="16">
@@ -12369,36 +12654,36 @@
         <v>6.0167814044666583</v>
       </c>
       <c r="D37" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0175184987845083</v>
       </c>
       <c r="E37" s="16">
         <v>1.2</v>
       </c>
       <c r="F37" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>382815.77696595591</v>
       </c>
       <c r="G37" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>165054.10773481819</v>
       </c>
       <c r="Q37" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>118.14969257403719</v>
       </c>
       <c r="R37" s="11">
         <v>0.7</v>
       </c>
       <c r="S37" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>119.93983943121955</v>
       </c>
       <c r="T37" s="11">
         <v>0.6</v>
       </c>
       <c r="U37" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.3</v>
       </c>
       <c r="V37" s="4">
@@ -12411,31 +12696,43 @@
       <c r="X37" s="4">
         <v>12397</v>
       </c>
-      <c r="AF37" s="11">
-        <f t="shared" si="18"/>
+      <c r="AF37" s="10">
+        <f t="shared" si="7"/>
+        <v>96.936741434590203</v>
+      </c>
+      <c r="AG37" s="11">
+        <f t="shared" si="13"/>
+        <v>96.936741434590203</v>
+      </c>
+      <c r="AH37" s="11">
+        <f t="shared" si="20"/>
         <v>96.68423568379643</v>
       </c>
-      <c r="AI37" s="11">
-        <f t="shared" si="19"/>
+      <c r="AJ37" s="11">
+        <f t="shared" si="21"/>
+        <v>-0.65451086265551339</v>
+      </c>
+      <c r="AK37" s="11">
+        <f t="shared" si="22"/>
         <v>119.48013160664161</v>
       </c>
-      <c r="AJ37" s="11">
+      <c r="AL37" s="11">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AN37" s="27">
-        <f t="shared" si="20"/>
+      <c r="AP37" s="27">
+        <f t="shared" si="23"/>
         <v>0.71206143811477352</v>
       </c>
-      <c r="AO37" s="29">
+      <c r="AQ37" s="29">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2031</v>
       </c>
       <c r="B38" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>731384.25576106412</v>
       </c>
       <c r="C38" s="16">
@@ -12443,36 +12740,36 @@
         <v>6.1230347578951854</v>
       </c>
       <c r="D38" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0176595003683611</v>
       </c>
       <c r="E38" s="16">
         <v>1.2</v>
       </c>
       <c r="F38" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>387409.56628954737</v>
       </c>
       <c r="G38" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>167034.75702763602</v>
       </c>
       <c r="Q38" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>118.97674042205544</v>
       </c>
       <c r="R38" s="11">
         <v>0.7</v>
       </c>
       <c r="S38" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>120.77941830723807</v>
       </c>
       <c r="T38" s="11">
         <v>0.5</v>
       </c>
       <c r="U38" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.3</v>
       </c>
       <c r="V38" s="4">
@@ -12485,31 +12782,43 @@
       <c r="X38" s="4">
         <v>12193</v>
       </c>
-      <c r="AF38" s="11">
-        <f t="shared" si="18"/>
+      <c r="AF38" s="10">
+        <f t="shared" si="7"/>
+        <v>96.237550154215569</v>
+      </c>
+      <c r="AG38" s="11">
+        <f t="shared" si="13"/>
+        <v>96.237550154215569</v>
+      </c>
+      <c r="AH38" s="11">
+        <f t="shared" si="20"/>
         <v>95.98686569240455</v>
       </c>
-      <c r="AI38" s="11">
-        <f t="shared" si="19"/>
+      <c r="AJ38" s="11">
+        <f t="shared" si="21"/>
+        <v>-0.72128613983421985</v>
+      </c>
+      <c r="AK38" s="11">
+        <f t="shared" si="22"/>
         <v>120.79441305431465</v>
       </c>
-      <c r="AJ38" s="11">
+      <c r="AL38" s="11">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AN38" s="27">
-        <f t="shared" si="20"/>
+      <c r="AP38" s="27">
+        <f t="shared" si="23"/>
         <v>0.71206143811477352</v>
       </c>
-      <c r="AO38" s="29">
+      <c r="AQ38" s="29">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2032</v>
       </c>
       <c r="B39" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>740160.86683019693</v>
       </c>
       <c r="C39" s="16">
@@ -12517,36 +12826,36 @@
         <v>6.2320939227573291</v>
       </c>
       <c r="D39" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0178112927942342</v>
       </c>
       <c r="E39" s="16">
         <v>1.2</v>
       </c>
       <c r="F39" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>392058.48108502192</v>
       </c>
       <c r="G39" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>169039.17411196764</v>
       </c>
       <c r="Q39" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>119.80957760500982</v>
       </c>
       <c r="R39" s="11">
         <v>0.7</v>
       </c>
       <c r="S39" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>121.62487423538873</v>
       </c>
       <c r="T39" s="11">
         <v>0.5</v>
       </c>
       <c r="U39" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.3</v>
       </c>
       <c r="V39" s="4">
@@ -12559,26 +12868,38 @@
       <c r="X39" s="4">
         <v>12026</v>
       </c>
-      <c r="AF39" s="11">
-        <f t="shared" si="18"/>
+      <c r="AF39" s="10">
+        <f t="shared" si="7"/>
+        <v>95.615128941889267</v>
+      </c>
+      <c r="AG39" s="11">
+        <f t="shared" si="13"/>
+        <v>95.615128941889267</v>
+      </c>
+      <c r="AH39" s="11">
+        <f t="shared" si="20"/>
         <v>95.366065794485991</v>
       </c>
-      <c r="AI39" s="11">
-        <f t="shared" si="19"/>
+      <c r="AJ39" s="11">
+        <f t="shared" si="21"/>
+        <v>-0.64675504657891736</v>
+      </c>
+      <c r="AK39" s="11">
+        <f t="shared" si="22"/>
         <v>122.1231515979121</v>
       </c>
-      <c r="AJ39" s="11">
+      <c r="AL39" s="11">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AN39" s="27">
-        <f t="shared" si="20"/>
+      <c r="AP39" s="27">
+        <f t="shared" si="23"/>
         <v>0.71206143811477352</v>
       </c>
-      <c r="AO39" s="29">
+      <c r="AQ39" s="29">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2033</v>
       </c>
@@ -12591,36 +12912,36 @@
         <v>6.3440031610823935</v>
       </c>
       <c r="D40" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0179569242235604</v>
       </c>
       <c r="E40" s="16">
         <v>1.2</v>
       </c>
       <c r="F40" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>396763.18285804219</v>
       </c>
       <c r="G40" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>171067.64420131125</v>
       </c>
       <c r="Q40" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>120.64824464824488</v>
       </c>
       <c r="R40" s="11">
         <v>0.7</v>
       </c>
       <c r="S40" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>122.47624835503643</v>
       </c>
       <c r="T40" s="11">
         <v>0.5</v>
       </c>
       <c r="U40" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.3</v>
       </c>
       <c r="V40" s="4">
@@ -12633,31 +12954,43 @@
       <c r="X40" s="4">
         <v>11879</v>
       </c>
-      <c r="AF40" s="11">
-        <f t="shared" si="18"/>
+      <c r="AF40" s="10">
+        <f t="shared" si="7"/>
+        <v>94.946763123939959</v>
+      </c>
+      <c r="AG40" s="11">
+        <f t="shared" si="13"/>
+        <v>94.946763123939959</v>
+      </c>
+      <c r="AH40" s="11">
+        <f t="shared" si="20"/>
         <v>94.699440969788242</v>
       </c>
-      <c r="AI40" s="11">
-        <f t="shared" si="19"/>
+      <c r="AJ40" s="11">
+        <f t="shared" si="21"/>
+        <v>-0.69901680345535055</v>
+      </c>
+      <c r="AK40" s="11">
+        <f t="shared" si="22"/>
         <v>123.46650626548912</v>
       </c>
-      <c r="AJ40" s="11">
+      <c r="AL40" s="11">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AN40" s="27">
-        <f t="shared" si="20"/>
+      <c r="AP40" s="27">
+        <f t="shared" si="23"/>
         <v>0.71206143811477352</v>
       </c>
-      <c r="AO40" s="29">
+      <c r="AQ40" s="29">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2034</v>
       </c>
       <c r="B41" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>757282.26800171298</v>
       </c>
       <c r="C41" s="16">
@@ -12665,36 +12998,36 @@
         <v>6.4525337673328078</v>
       </c>
       <c r="D41" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0171075901910329</v>
       </c>
       <c r="E41" s="16">
         <v>1.1000000000000001</v>
       </c>
       <c r="F41" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>401127.57786948059</v>
       </c>
       <c r="G41" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>172949.38828752565</v>
       </c>
       <c r="Q41" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>121.49278236078258</v>
       </c>
       <c r="R41" s="11">
         <v>0.7</v>
       </c>
       <c r="S41" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>123.33358209352167</v>
       </c>
       <c r="T41" s="11">
         <v>0.4</v>
       </c>
       <c r="U41" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.3</v>
       </c>
       <c r="V41" s="4">
@@ -12707,31 +13040,43 @@
       <c r="X41" s="4">
         <v>11771</v>
       </c>
-      <c r="AF41" s="11">
-        <f t="shared" si="18"/>
+      <c r="AF41" s="10">
+        <f t="shared" si="7"/>
+        <v>94.229893138654646</v>
+      </c>
+      <c r="AG41" s="11">
+        <f t="shared" si="13"/>
+        <v>94.229893138654646</v>
+      </c>
+      <c r="AH41" s="11">
+        <f t="shared" si="20"/>
         <v>93.984438323874741</v>
       </c>
-      <c r="AI41" s="11">
-        <f t="shared" si="19"/>
+      <c r="AJ41" s="11">
+        <f t="shared" si="21"/>
+        <v>-0.75502309051815075</v>
+      </c>
+      <c r="AK41" s="11">
+        <f t="shared" si="22"/>
         <v>124.82463783440949</v>
       </c>
-      <c r="AJ41" s="11">
+      <c r="AL41" s="11">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AN41" s="27">
-        <f t="shared" si="20"/>
+      <c r="AP41" s="27">
+        <f t="shared" si="23"/>
         <v>0.71206143811477352</v>
       </c>
-      <c r="AO41" s="29">
+      <c r="AQ41" s="29">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2035</v>
       </c>
       <c r="B42" s="20">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>765612.37294973177</v>
       </c>
       <c r="C42" s="20">
@@ -12739,36 +13084,36 @@
         <v>6.5639483616091683</v>
       </c>
       <c r="D42" s="22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0172667975548486</v>
       </c>
       <c r="E42" s="20">
         <v>1.1000000000000001</v>
       </c>
       <c r="F42" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>405539.98122604482</v>
       </c>
       <c r="G42" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>174851.83155868843</v>
       </c>
       <c r="Q42" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>122.34323183730805</v>
       </c>
       <c r="R42" s="24">
         <v>0.7</v>
       </c>
       <c r="S42" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>124.19691716817631</v>
       </c>
       <c r="T42" s="24">
         <v>0.4</v>
       </c>
       <c r="U42" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.3</v>
       </c>
       <c r="V42" s="4">
@@ -12781,26 +13126,38 @@
       <c r="X42" s="4">
         <v>11691</v>
       </c>
-      <c r="AF42" s="11">
-        <f t="shared" si="18"/>
+      <c r="AF42" s="10">
+        <f t="shared" si="7"/>
+        <v>93.533725506439424</v>
+      </c>
+      <c r="AG42" s="11">
+        <f t="shared" si="13"/>
+        <v>93.533725506439424</v>
+      </c>
+      <c r="AH42" s="11">
+        <f t="shared" si="20"/>
         <v>93.290084104489878</v>
       </c>
-      <c r="AI42" s="11">
-        <f t="shared" si="19"/>
+      <c r="AJ42" s="11">
+        <f t="shared" si="21"/>
+        <v>-0.73879700913047941</v>
+      </c>
+      <c r="AK42" s="11">
+        <f t="shared" si="22"/>
         <v>126.19770885058797</v>
       </c>
-      <c r="AJ42" s="24">
+      <c r="AL42" s="24">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AN42" s="27">
-        <f t="shared" si="20"/>
+      <c r="AP42" s="27">
+        <f t="shared" si="23"/>
         <v>0.71206143811477352</v>
       </c>
-      <c r="AO42" s="29">
+      <c r="AQ42" s="29">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2036</v>
       </c>
@@ -12817,15 +13174,15 @@
         <v>1.0839053577294635</v>
       </c>
       <c r="F43" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>409935.65081028896</v>
       </c>
       <c r="G43" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>176747.05992904116</v>
       </c>
       <c r="Q43" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>123.19963446016919</v>
       </c>
       <c r="R43" s="11">
@@ -12833,7 +13190,7 @@
         <v>0.7</v>
       </c>
       <c r="S43" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>125.06629558835354</v>
       </c>
       <c r="T43" s="11">
@@ -12841,7 +13198,7 @@
         <v>0.4</v>
       </c>
       <c r="U43" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.3</v>
       </c>
       <c r="V43" s="4">
@@ -12854,27 +13211,39 @@
       <c r="X43" s="4">
         <v>11605</v>
       </c>
-      <c r="AF43" s="11">
-        <f t="shared" si="18"/>
+      <c r="AF43" s="10">
+        <f t="shared" si="7"/>
+        <v>92.879787083326775</v>
+      </c>
+      <c r="AG43" s="11">
+        <f t="shared" si="13"/>
+        <v>92.879787083326775</v>
+      </c>
+      <c r="AH43" s="11">
+        <f t="shared" si="20"/>
         <v>92.637849093417458</v>
       </c>
-      <c r="AI43" s="11">
-        <f t="shared" si="19"/>
+      <c r="AJ43" s="11">
+        <f t="shared" si="21"/>
+        <v>-0.69914720019104948</v>
+      </c>
+      <c r="AK43" s="11">
+        <f t="shared" si="22"/>
         <v>127.58588364794443</v>
       </c>
-      <c r="AJ43" s="11">
-        <f>AJ42</f>
+      <c r="AL43" s="11">
+        <f>AL42</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="AN43" s="27">
-        <f t="shared" si="20"/>
+      <c r="AP43" s="27">
+        <f t="shared" si="23"/>
         <v>0.71206143811477352</v>
       </c>
-      <c r="AO43" s="29">
+      <c r="AQ43" s="29">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2037</v>
       </c>
@@ -12883,39 +13252,39 @@
         <v>782179.41251643701</v>
       </c>
       <c r="D44" s="23">
-        <f t="shared" ref="D44:D47" si="21">D43</f>
+        <f t="shared" ref="D44:D47" si="24">D43</f>
         <v>1.0172667975548486</v>
       </c>
       <c r="E44" s="17">
-        <f t="shared" ref="E44:E47" si="22">B44/B43*100-100</f>
+        <f t="shared" ref="E44:E47" si="25">B44/B43*100-100</f>
         <v>1.0684080275024996</v>
       </c>
       <c r="F44" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>414315.43621114071</v>
       </c>
       <c r="G44" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>178635.4397056977</v>
       </c>
       <c r="Q44" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>124.06203190139037</v>
       </c>
       <c r="R44" s="11">
-        <f t="shared" ref="R44:R47" si="23">R43</f>
+        <f t="shared" ref="R44:R47" si="26">R43</f>
         <v>0.7</v>
       </c>
       <c r="S44" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>125.94175965747201</v>
       </c>
       <c r="T44" s="11">
-        <f t="shared" ref="T44:T47" si="24">T43</f>
+        <f t="shared" ref="T44:T47" si="27">T43</f>
         <v>0.4</v>
       </c>
       <c r="U44" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.3</v>
       </c>
       <c r="V44" s="4">
@@ -12928,27 +13297,39 @@
       <c r="X44" s="4">
         <v>11551</v>
       </c>
-      <c r="AF44" s="11">
-        <f t="shared" si="18"/>
+      <c r="AF44" s="10">
+        <f t="shared" si="7"/>
+        <v>92.215274119461711</v>
+      </c>
+      <c r="AG44" s="11">
+        <f t="shared" si="13"/>
+        <v>92.215274119461711</v>
+      </c>
+      <c r="AH44" s="11">
+        <f t="shared" si="20"/>
         <v>91.975067086693841</v>
       </c>
-      <c r="AI44" s="11">
-        <f t="shared" si="19"/>
+      <c r="AJ44" s="11">
+        <f t="shared" si="21"/>
+        <v>-0.71545487423317411</v>
+      </c>
+      <c r="AK44" s="11">
+        <f t="shared" si="22"/>
         <v>128.9893283680718</v>
       </c>
-      <c r="AJ44" s="11">
-        <f t="shared" ref="AJ44:AJ47" si="25">AJ43</f>
+      <c r="AL44" s="11">
+        <f t="shared" ref="AL44:AL47" si="28">AL43</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="AN44" s="27">
-        <f t="shared" si="20"/>
+      <c r="AP44" s="27">
+        <f t="shared" si="23"/>
         <v>0.71206143811477352</v>
       </c>
-      <c r="AO44" s="29">
+      <c r="AQ44" s="29">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2038</v>
       </c>
@@ -12957,39 +13338,39 @@
         <v>790426.73636312608</v>
       </c>
       <c r="D45" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>1.0172667975548486</v>
       </c>
       <c r="E45" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>1.0544030838341314</v>
       </c>
       <c r="F45" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>418683.99094735179</v>
       </c>
       <c r="G45" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>180518.97729077525</v>
       </c>
       <c r="Q45" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>124.93046612470009</v>
       </c>
       <c r="R45" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.7</v>
       </c>
       <c r="S45" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>126.8233519750743</v>
       </c>
       <c r="T45" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0.4</v>
       </c>
       <c r="U45" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.3</v>
       </c>
       <c r="V45" s="4">
@@ -13002,27 +13383,39 @@
       <c r="X45" s="4">
         <v>11520</v>
       </c>
-      <c r="AF45" s="11">
-        <f t="shared" si="18"/>
+      <c r="AF45" s="10">
+        <f t="shared" si="7"/>
+        <v>91.623896894073098</v>
+      </c>
+      <c r="AG45" s="11">
+        <f t="shared" si="13"/>
+        <v>91.623896894073098</v>
+      </c>
+      <c r="AH45" s="11">
+        <f t="shared" si="20"/>
         <v>91.385230310758033</v>
       </c>
-      <c r="AI45" s="11">
-        <f t="shared" si="19"/>
+      <c r="AJ45" s="11">
+        <f t="shared" si="21"/>
+        <v>-0.64130072922897341</v>
+      </c>
+      <c r="AK45" s="11">
+        <f t="shared" si="22"/>
         <v>130.40821098012057</v>
       </c>
-      <c r="AJ45" s="11">
-        <f t="shared" si="25"/>
+      <c r="AL45" s="11">
+        <f t="shared" si="28"/>
         <v>1.1000000000000001</v>
       </c>
-      <c r="AN45" s="27">
-        <f t="shared" si="20"/>
+      <c r="AP45" s="27">
+        <f t="shared" si="23"/>
         <v>0.71206143811477352</v>
       </c>
-      <c r="AO45" s="29">
+      <c r="AQ45" s="29">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2039</v>
       </c>
@@ -13031,39 +13424,39 @@
         <v>798648.3482101839</v>
       </c>
       <c r="D46" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>1.0172667975548486</v>
       </c>
       <c r="E46" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>1.0401485006550644</v>
       </c>
       <c r="F46" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>423038.92620167346</v>
       </c>
       <c r="G46" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>182396.64272646309</v>
       </c>
       <c r="Q46" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>125.80497938757297</v>
       </c>
       <c r="R46" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.7</v>
       </c>
       <c r="S46" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>127.71111543889981</v>
       </c>
       <c r="T46" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0.4</v>
       </c>
       <c r="U46" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.3</v>
       </c>
       <c r="V46" s="4">
@@ -13076,27 +13469,39 @@
       <c r="X46" s="4">
         <v>11474</v>
       </c>
-      <c r="AF46" s="11">
-        <f t="shared" si="18"/>
+      <c r="AF46" s="10">
+        <f t="shared" si="7"/>
+        <v>91.030114677554849</v>
+      </c>
+      <c r="AG46" s="11">
+        <f t="shared" si="13"/>
+        <v>91.030114677554849</v>
+      </c>
+      <c r="AH46" s="11">
+        <f t="shared" si="20"/>
         <v>90.792994808335706</v>
       </c>
-      <c r="AI46" s="11">
-        <f t="shared" si="19"/>
+      <c r="AJ46" s="11">
+        <f t="shared" si="21"/>
+        <v>-0.64806479166098541</v>
+      </c>
+      <c r="AK46" s="11">
+        <f t="shared" si="22"/>
         <v>131.84270130090189</v>
       </c>
-      <c r="AJ46" s="11">
-        <f t="shared" si="25"/>
+      <c r="AL46" s="11">
+        <f t="shared" si="28"/>
         <v>1.1000000000000001</v>
       </c>
-      <c r="AN46" s="27">
-        <f t="shared" si="20"/>
+      <c r="AP46" s="27">
+        <f t="shared" si="23"/>
         <v>0.71206143811477352</v>
       </c>
-      <c r="AO46" s="29">
+      <c r="AQ46" s="29">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2040</v>
       </c>
@@ -13105,39 +13510,39 @@
         <v>806846.71671906847</v>
       </c>
       <c r="D47" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>1.0172667975548486</v>
       </c>
       <c r="E47" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>1.0265304532661474</v>
       </c>
       <c r="F47" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>427381.54960830376</v>
       </c>
       <c r="G47" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>184268.99980978528</v>
       </c>
       <c r="Q47" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>126.68561424328597</v>
       </c>
       <c r="R47" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.7</v>
       </c>
       <c r="S47" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>128.6050932469721</v>
       </c>
       <c r="T47" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>0.4</v>
       </c>
       <c r="U47" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.3</v>
       </c>
       <c r="V47" s="4">
@@ -13150,27 +13555,39 @@
       <c r="X47" s="4">
         <v>11419</v>
       </c>
-      <c r="AF47" s="11">
-        <f t="shared" si="18"/>
+      <c r="AF47" s="10">
+        <f t="shared" si="7"/>
+        <v>90.403796481539672</v>
+      </c>
+      <c r="AG47" s="11">
+        <f t="shared" si="13"/>
+        <v>90.403796481539672</v>
+      </c>
+      <c r="AH47" s="11">
+        <f t="shared" si="20"/>
         <v>90.168308077789462</v>
       </c>
-      <c r="AI47" s="11">
-        <f t="shared" si="19"/>
+      <c r="AJ47" s="11">
+        <f t="shared" si="21"/>
+        <v>-0.6880340623910115</v>
+      </c>
+      <c r="AK47" s="11">
+        <f t="shared" si="22"/>
         <v>133.2929710152118</v>
       </c>
-      <c r="AJ47" s="11">
-        <f t="shared" si="25"/>
+      <c r="AL47" s="11">
+        <f t="shared" si="28"/>
         <v>1.1000000000000001</v>
       </c>
-      <c r="AN47" s="27">
-        <f t="shared" si="20"/>
+      <c r="AP47" s="27">
+        <f t="shared" si="23"/>
         <v>0.71206143811477352</v>
       </c>
-      <c r="AO47" s="29">
+      <c r="AQ47" s="29">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2041</v>
       </c>
@@ -13460,7 +13877,7 @@
         <v>2060</v>
       </c>
       <c r="V67" s="4">
-        <f t="shared" ref="V67:V77" si="26">W67-X67</f>
+        <f t="shared" ref="V67:V77" si="29">W67-X67</f>
         <v>87218</v>
       </c>
       <c r="W67" s="4">
@@ -13475,7 +13892,7 @@
         <v>2061</v>
       </c>
       <c r="V68" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>86449</v>
       </c>
       <c r="W68" s="4">
@@ -13490,7 +13907,7 @@
         <v>2062</v>
       </c>
       <c r="V69" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>85665</v>
       </c>
       <c r="W69" s="4">
@@ -13505,7 +13922,7 @@
         <v>2063</v>
       </c>
       <c r="V70" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>84865</v>
       </c>
       <c r="W70" s="4">
@@ -13520,7 +13937,7 @@
         <v>2064</v>
       </c>
       <c r="V71" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>84052</v>
       </c>
       <c r="W71" s="4">
@@ -13535,7 +13952,7 @@
         <v>2065</v>
       </c>
       <c r="V72" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>83227</v>
       </c>
       <c r="W72" s="4">
@@ -13550,7 +13967,7 @@
         <v>2066</v>
       </c>
       <c r="V73" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>82393</v>
       </c>
       <c r="W73" s="4">
@@ -13565,7 +13982,7 @@
         <v>2067</v>
       </c>
       <c r="V74" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>81551</v>
       </c>
       <c r="W74" s="4">
@@ -13580,7 +13997,7 @@
         <v>2068</v>
       </c>
       <c r="V75" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>80706</v>
       </c>
       <c r="W75" s="4">
@@ -13595,7 +14012,7 @@
         <v>2069</v>
       </c>
       <c r="V76" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>79862</v>
       </c>
       <c r="W76" s="4">
@@ -13610,7 +14027,7 @@
         <v>2070</v>
       </c>
       <c r="V77" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>79021</v>
       </c>
       <c r="W77" s="4">
@@ -13623,8 +14040,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -13740,6 +14156,5 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>